--- a/examples/report.xlsx
+++ b/examples/report.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Quality" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Calc" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Quality" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,8 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="£#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="£0.00"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,10 +34,24 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <color rgb="0044546A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,11 +60,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -53,16 +77,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7C9E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7C9E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7C9E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7C9E0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -152,7 +204,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Books per category (top 12)</a:t>
+              <a:t>Top 10 categories by titles</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -167,22 +219,25 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Summary'!B1</f>
+              <f>'Calc'!B1</f>
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2E86AB"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Summary'!$A$2:$A$13</f>
+              <f>'Calc'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$B$2:$B$13</f>
+              <f>'Calc'!$B$2:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -219,16 +274,159 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Price distribution</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Calc'!B12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="F18F01"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Calc'!$A$13:$A$17</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Calc'!$B$13:$B$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Rating distribution</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <doughnutChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Calc'!B19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Calc'!$A$20:$A$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Calc'!$B$20:$B$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showPercent val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+        <holeSize val="10"/>
+      </doughnutChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="3240000"/>
+    <ext cx="5400000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -238,6 +436,50 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3960000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -535,6 +777,369 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Catalog analytics — books.toscrape.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>BOOKS</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>CATEGORIES</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>AVG PRICE</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>MEDIAN PRICE</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>IN STOCK</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>RATED 4-5</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>517</v>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="5" t="n">
+        <v>35.32</v>
+      </c>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="5" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="6" t="n">
+        <v>0.3713733075435203</v>
+      </c>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="P3:R3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Historical Fiction</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sequential Art</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Romance</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fiction</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Childrens</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Nonfiction</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Add a comment</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Price band</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>£0-20</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>£20-30</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>£30-40</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>£40-50</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>£50-100</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1 star</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2 stars</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3 stars</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4 stars</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>5 stars</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -547,32 +1152,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Rating</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>In stock</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
@@ -589,7 +1194,7 @@
           <t>Academic</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="8" t="n">
         <v>13.12</v>
       </c>
       <c r="D2" t="n">
@@ -617,7 +1222,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="8" t="n">
         <v>55.51</v>
       </c>
       <c r="D3" t="n">
@@ -645,7 +1250,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="8" t="n">
         <v>40.79</v>
       </c>
       <c r="D4" t="n">
@@ -673,7 +1278,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="8" t="n">
         <v>56.48</v>
       </c>
       <c r="D5" t="n">
@@ -701,7 +1306,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="8" t="n">
         <v>34.2</v>
       </c>
       <c r="D6" t="n">
@@ -729,7 +1334,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="8" t="n">
         <v>20.29</v>
       </c>
       <c r="D7" t="n">
@@ -757,7 +1362,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="8" t="n">
         <v>22.13</v>
       </c>
       <c r="D8" t="n">
@@ -785,7 +1390,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="8" t="n">
         <v>53.9</v>
       </c>
       <c r="D9" t="n">
@@ -813,7 +1418,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="8" t="n">
         <v>28.26</v>
       </c>
       <c r="D10" t="n">
@@ -841,7 +1446,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="8" t="n">
         <v>37.61</v>
       </c>
       <c r="D11" t="n">
@@ -869,7 +1474,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="8" t="n">
         <v>14.07</v>
       </c>
       <c r="D12" t="n">
@@ -897,7 +1502,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="8" t="n">
         <v>37.86</v>
       </c>
       <c r="D13" t="n">
@@ -925,7 +1530,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="8" t="n">
         <v>29.06</v>
       </c>
       <c r="D14" t="n">
@@ -953,7 +1558,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="8" t="n">
         <v>40.76</v>
       </c>
       <c r="D15" t="n">
@@ -981,7 +1586,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" s="8" t="n">
         <v>48.78</v>
       </c>
       <c r="D16" t="n">
@@ -1009,7 +1614,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" s="8" t="n">
         <v>40.67</v>
       </c>
       <c r="D17" t="n">
@@ -1037,7 +1642,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="D18" t="n">
@@ -1065,7 +1670,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C19" s="8" t="n">
         <v>23.89</v>
       </c>
       <c r="D19" t="n">
@@ -1093,7 +1698,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C20" s="8" t="n">
         <v>37.4</v>
       </c>
       <c r="D20" t="n">
@@ -1121,7 +1726,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C21" s="8" t="n">
         <v>19.09</v>
       </c>
       <c r="D21" t="n">
@@ -1149,7 +1754,7 @@
           <t>Add a comment</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C22" s="8" t="n">
         <v>25.91</v>
       </c>
       <c r="D22" t="n">
@@ -1177,7 +1782,7 @@
           <t>Adult Fiction</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" s="8" t="n">
         <v>15.36</v>
       </c>
       <c r="D23" t="n">
@@ -1205,7 +1810,7 @@
           <t>Art</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="8" t="n">
         <v>48.63</v>
       </c>
       <c r="D24" t="n">
@@ -1233,7 +1838,7 @@
           <t>Art</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" s="8" t="n">
         <v>49.05</v>
       </c>
       <c r="D25" t="n">
@@ -1261,7 +1866,7 @@
           <t>Art</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="8" t="n">
         <v>10.29</v>
       </c>
       <c r="D26" t="n">
@@ -1289,7 +1894,7 @@
           <t>Art</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C27" s="8" t="n">
         <v>32.34</v>
       </c>
       <c r="D27" t="n">
@@ -1317,7 +1922,7 @@
           <t>Art</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C28" s="8" t="n">
         <v>43.02</v>
       </c>
       <c r="D28" t="n">
@@ -1345,7 +1950,7 @@
           <t>Art</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C29" s="8" t="n">
         <v>41.14</v>
       </c>
       <c r="D29" t="n">
@@ -1373,7 +1978,7 @@
           <t>Art</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C30" s="8" t="n">
         <v>44.18</v>
       </c>
       <c r="D30" t="n">
@@ -1401,7 +2006,7 @@
           <t>Art</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C31" s="8" t="n">
         <v>39.51</v>
       </c>
       <c r="D31" t="n">
@@ -1429,7 +2034,7 @@
           <t>Autobiography</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C32" s="8" t="n">
         <v>54.29</v>
       </c>
       <c r="D32" t="n">
@@ -1457,7 +2062,7 @@
           <t>Autobiography</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
+      <c r="C33" s="8" t="n">
         <v>58.81</v>
       </c>
       <c r="D33" t="n">
@@ -1485,7 +2090,7 @@
           <t>Autobiography</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
+      <c r="C34" s="8" t="n">
         <v>40.85</v>
       </c>
       <c r="D34" t="n">
@@ -1513,7 +2118,7 @@
           <t>Autobiography</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
+      <c r="C35" s="8" t="n">
         <v>59.04</v>
       </c>
       <c r="D35" t="n">
@@ -1541,7 +2146,7 @@
           <t>Autobiography</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C36" s="8" t="n">
         <v>11.87</v>
       </c>
       <c r="D36" t="n">
@@ -1569,7 +2174,7 @@
           <t>Autobiography</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C37" s="8" t="n">
         <v>27.18</v>
       </c>
       <c r="D37" t="n">
@@ -1597,7 +2202,7 @@
           <t>Autobiography</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C38" s="8" t="n">
         <v>57.6</v>
       </c>
       <c r="D38" t="n">
@@ -1625,7 +2230,7 @@
           <t>Autobiography</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
+      <c r="C39" s="8" t="n">
         <v>12.91</v>
       </c>
       <c r="D39" t="n">
@@ -1653,7 +2258,7 @@
           <t>Autobiography</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
+      <c r="C40" s="8" t="n">
         <v>10.93</v>
       </c>
       <c r="D40" t="n">
@@ -1681,7 +2286,7 @@
           <t>Biography</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
+      <c r="C41" s="8" t="n">
         <v>48.19</v>
       </c>
       <c r="D41" t="n">
@@ -1709,7 +2314,7 @@
           <t>Biography</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="C42" s="8" t="n">
         <v>16.85</v>
       </c>
       <c r="D42" t="n">
@@ -1737,7 +2342,7 @@
           <t>Biography</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
+      <c r="C43" s="8" t="n">
         <v>21.15</v>
       </c>
       <c r="D43" t="n">
@@ -1765,7 +2370,7 @@
           <t>Biography</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
+      <c r="C44" s="8" t="n">
         <v>39.55</v>
       </c>
       <c r="D44" t="n">
@@ -1793,7 +2398,7 @@
           <t>Biography</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
+      <c r="C45" s="8" t="n">
         <v>42.57</v>
       </c>
       <c r="D45" t="n">
@@ -1821,7 +2426,7 @@
           <t>Business</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C46" s="8" t="n">
         <v>21.59</v>
       </c>
       <c r="D46" t="n">
@@ -1849,7 +2454,7 @@
           <t>Business</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C47" s="8" t="n">
         <v>38.85</v>
       </c>
       <c r="D47" t="n">
@@ -1877,7 +2482,7 @@
           <t>Business</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
+      <c r="C48" s="8" t="n">
         <v>43.14</v>
       </c>
       <c r="D48" t="n">
@@ -1905,7 +2510,7 @@
           <t>Business</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C49" s="8" t="n">
         <v>44.88</v>
       </c>
       <c r="D49" t="n">
@@ -1933,7 +2538,7 @@
           <t>Business</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C50" s="8" t="n">
         <v>51.74</v>
       </c>
       <c r="D50" t="n">
@@ -1961,7 +2566,7 @@
           <t>Business</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
+      <c r="C51" s="8" t="n">
         <v>23.99</v>
       </c>
       <c r="D51" t="n">
@@ -1989,7 +2594,7 @@
           <t>Business</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
+      <c r="C52" s="8" t="n">
         <v>27.55</v>
       </c>
       <c r="D52" t="n">
@@ -2017,7 +2622,7 @@
           <t>Business</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
+      <c r="C53" s="8" t="n">
         <v>21</v>
       </c>
       <c r="D53" t="n">
@@ -2045,7 +2650,7 @@
           <t>Business</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
+      <c r="C54" s="8" t="n">
         <v>33.34</v>
       </c>
       <c r="D54" t="n">
@@ -2073,7 +2678,7 @@
           <t>Business</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
+      <c r="C55" s="8" t="n">
         <v>36.91</v>
       </c>
       <c r="D55" t="n">
@@ -2101,7 +2706,7 @@
           <t>Business</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
+      <c r="C56" s="8" t="n">
         <v>33.92</v>
       </c>
       <c r="D56" t="n">
@@ -2129,7 +2734,7 @@
           <t>Business</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
+      <c r="C57" s="8" t="n">
         <v>12.61</v>
       </c>
       <c r="D57" t="n">
@@ -2157,7 +2762,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
+      <c r="C58" s="8" t="n">
         <v>54.64</v>
       </c>
       <c r="D58" t="n">
@@ -2185,7 +2790,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
+      <c r="C59" s="8" t="n">
         <v>13.47</v>
       </c>
       <c r="D59" t="n">
@@ -2213,7 +2818,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
+      <c r="C60" s="8" t="n">
         <v>53.95</v>
       </c>
       <c r="D60" t="n">
@@ -2241,7 +2846,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
+      <c r="C61" s="8" t="n">
         <v>22.54</v>
       </c>
       <c r="D61" t="n">
@@ -2269,7 +2874,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
+      <c r="C62" s="8" t="n">
         <v>25.08</v>
       </c>
       <c r="D62" t="n">
@@ -2297,7 +2902,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n">
+      <c r="C63" s="8" t="n">
         <v>18.28</v>
       </c>
       <c r="D63" t="n">
@@ -2325,7 +2930,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
+      <c r="C64" s="8" t="n">
         <v>32.38</v>
       </c>
       <c r="D64" t="n">
@@ -2353,7 +2958,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
+      <c r="C65" s="8" t="n">
         <v>23.57</v>
       </c>
       <c r="D65" t="n">
@@ -2381,7 +2986,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
+      <c r="C66" s="8" t="n">
         <v>34.41</v>
       </c>
       <c r="D66" t="n">
@@ -2409,7 +3014,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
+      <c r="C67" s="8" t="n">
         <v>52.87</v>
       </c>
       <c r="D67" t="n">
@@ -2437,7 +3042,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
+      <c r="C68" s="8" t="n">
         <v>36.89</v>
       </c>
       <c r="D68" t="n">
@@ -2465,7 +3070,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
+      <c r="C69" s="8" t="n">
         <v>26.33</v>
       </c>
       <c r="D69" t="n">
@@ -2493,7 +3098,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n">
+      <c r="C70" s="8" t="n">
         <v>43.59</v>
       </c>
       <c r="D70" t="n">
@@ -2521,7 +3126,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
+      <c r="C71" s="8" t="n">
         <v>56.13</v>
       </c>
       <c r="D71" t="n">
@@ -2549,7 +3154,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
+      <c r="C72" s="8" t="n">
         <v>48.77</v>
       </c>
       <c r="D72" t="n">
@@ -2577,7 +3182,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n">
+      <c r="C73" s="8" t="n">
         <v>35.96</v>
       </c>
       <c r="D73" t="n">
@@ -2605,7 +3210,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
+      <c r="C74" s="8" t="n">
         <v>58.08</v>
       </c>
       <c r="D74" t="n">
@@ -2633,7 +3238,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
+      <c r="C75" s="8" t="n">
         <v>56.07</v>
       </c>
       <c r="D75" t="n">
@@ -2661,7 +3266,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
+      <c r="C76" s="8" t="n">
         <v>22.08</v>
       </c>
       <c r="D76" t="n">
@@ -2689,7 +3294,7 @@
           <t>Childrens</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
+      <c r="C77" s="8" t="n">
         <v>12.96</v>
       </c>
       <c r="D77" t="n">
@@ -2717,7 +3322,7 @@
           <t>Christian</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
+      <c r="C78" s="8" t="n">
         <v>54</v>
       </c>
       <c r="D78" t="n">
@@ -2745,7 +3350,7 @@
           <t>Christian</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
+      <c r="C79" s="8" t="n">
         <v>25.77</v>
       </c>
       <c r="D79" t="n">
@@ -2773,7 +3378,7 @@
           <t>Christian</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
+      <c r="C80" s="8" t="n">
         <v>47.72</v>
       </c>
       <c r="D80" t="n">
@@ -2801,7 +3406,7 @@
           <t>Christian Fiction</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
+      <c r="C81" s="8" t="n">
         <v>49.46</v>
       </c>
       <c r="D81" t="n">
@@ -2829,7 +3434,7 @@
           <t>Christian Fiction</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
+      <c r="C82" s="8" t="n">
         <v>17.97</v>
       </c>
       <c r="D82" t="n">
@@ -2857,7 +3462,7 @@
           <t>Christian Fiction</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n">
+      <c r="C83" s="8" t="n">
         <v>49.97</v>
       </c>
       <c r="D83" t="n">
@@ -2885,7 +3490,7 @@
           <t>Christian Fiction</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
+      <c r="C84" s="8" t="n">
         <v>28.77</v>
       </c>
       <c r="D84" t="n">
@@ -2913,7 +3518,7 @@
           <t>Christian Fiction</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
+      <c r="C85" s="8" t="n">
         <v>20.47</v>
       </c>
       <c r="D85" t="n">
@@ -2941,7 +3546,7 @@
           <t>Christian Fiction</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
+      <c r="C86" s="8" t="n">
         <v>39.67</v>
       </c>
       <c r="D86" t="n">
@@ -2969,7 +3574,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
+      <c r="C87" s="8" t="n">
         <v>55.53</v>
       </c>
       <c r="D87" t="n">
@@ -2997,7 +3602,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
+      <c r="C88" s="8" t="n">
         <v>35.01</v>
       </c>
       <c r="D88" t="n">
@@ -3025,7 +3630,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n">
+      <c r="C89" s="8" t="n">
         <v>57.22</v>
       </c>
       <c r="D89" t="n">
@@ -3053,7 +3658,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
+      <c r="C90" s="8" t="n">
         <v>38.35</v>
       </c>
       <c r="D90" t="n">
@@ -3081,7 +3686,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n">
+      <c r="C91" s="8" t="n">
         <v>58.63</v>
       </c>
       <c r="D91" t="n">
@@ -3109,7 +3714,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n">
+      <c r="C92" s="8" t="n">
         <v>32.93</v>
       </c>
       <c r="D92" t="n">
@@ -3137,7 +3742,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n">
+      <c r="C93" s="8" t="n">
         <v>32.49</v>
       </c>
       <c r="D93" t="n">
@@ -3165,7 +3770,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
+      <c r="C94" s="8" t="n">
         <v>28.07</v>
       </c>
       <c r="D94" t="n">
@@ -3193,7 +3798,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n">
+      <c r="C95" s="8" t="n">
         <v>47.11</v>
       </c>
       <c r="D95" t="n">
@@ -3221,7 +3826,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
+      <c r="C96" s="8" t="n">
         <v>37.46</v>
       </c>
       <c r="D96" t="n">
@@ -3249,7 +3854,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n">
+      <c r="C97" s="8" t="n">
         <v>26.78</v>
       </c>
       <c r="D97" t="n">
@@ -3277,7 +3882,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
+      <c r="C98" s="8" t="n">
         <v>14.82</v>
       </c>
       <c r="D98" t="n">
@@ -3305,7 +3910,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
+      <c r="C99" s="8" t="n">
         <v>45.42</v>
       </c>
       <c r="D99" t="n">
@@ -3333,7 +3938,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
+      <c r="C100" s="8" t="n">
         <v>28.58</v>
       </c>
       <c r="D100" t="n">
@@ -3361,7 +3966,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n">
+      <c r="C101" s="8" t="n">
         <v>29.7</v>
       </c>
       <c r="D101" t="n">
@@ -3389,7 +3994,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
+      <c r="C102" s="8" t="n">
         <v>50.26</v>
       </c>
       <c r="D102" t="n">
@@ -3417,7 +4022,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
+      <c r="C103" s="8" t="n">
         <v>15.08</v>
       </c>
       <c r="D103" t="n">
@@ -3445,7 +4050,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
+      <c r="C104" s="8" t="n">
         <v>43.19</v>
       </c>
       <c r="D104" t="n">
@@ -3473,7 +4078,7 @@
           <t>Classics</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
+      <c r="C105" s="8" t="n">
         <v>17.73</v>
       </c>
       <c r="D105" t="n">
@@ -3501,7 +4106,7 @@
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
+      <c r="C106" s="8" t="n">
         <v>52.79</v>
       </c>
       <c r="D106" t="n">
@@ -3529,7 +4134,7 @@
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
+      <c r="C107" s="8" t="n">
         <v>24.04</v>
       </c>
       <c r="D107" t="n">
@@ -3557,7 +4162,7 @@
           <t>Contemporary</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n">
+      <c r="C108" s="8" t="n">
         <v>31.77</v>
       </c>
       <c r="D108" t="n">
@@ -3585,7 +4190,7 @@
           <t>Crime</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n">
+      <c r="C109" s="8" t="n">
         <v>10.97</v>
       </c>
       <c r="D109" t="n">
@@ -3613,7 +4218,7 @@
           <t>Cultural</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n">
+      <c r="C110" s="8" t="n">
         <v>36.58</v>
       </c>
       <c r="D110" t="n">
@@ -3641,7 +4246,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
+      <c r="C111" s="8" t="n">
         <v>56.76</v>
       </c>
       <c r="D111" t="n">
@@ -3669,7 +4274,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n">
+      <c r="C112" s="8" t="n">
         <v>42.95</v>
       </c>
       <c r="D112" t="n">
@@ -3697,7 +4302,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n">
+      <c r="C113" s="8" t="n">
         <v>53.13</v>
       </c>
       <c r="D113" t="n">
@@ -3725,7 +4330,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
+      <c r="C114" s="8" t="n">
         <v>22.5</v>
       </c>
       <c r="D114" t="n">
@@ -3753,7 +4358,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
+      <c r="C115" s="8" t="n">
         <v>49.46</v>
       </c>
       <c r="D115" t="n">
@@ -3781,7 +4386,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
+      <c r="C116" s="8" t="n">
         <v>18.02</v>
       </c>
       <c r="D116" t="n">
@@ -3809,7 +4414,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
+      <c r="C117" s="8" t="n">
         <v>33.29</v>
       </c>
       <c r="D117" t="n">
@@ -3837,7 +4442,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n">
+      <c r="C118" s="8" t="n">
         <v>39.58</v>
       </c>
       <c r="D118" t="n">
@@ -3865,7 +4470,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n">
+      <c r="C119" s="8" t="n">
         <v>13.99</v>
       </c>
       <c r="D119" t="n">
@@ -3893,7 +4498,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n">
+      <c r="C120" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="D120" t="n">
@@ -3921,7 +4526,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n">
+      <c r="C121" s="8" t="n">
         <v>32</v>
       </c>
       <c r="D121" t="n">
@@ -3949,7 +4554,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n">
+      <c r="C122" s="8" t="n">
         <v>17.93</v>
       </c>
       <c r="D122" t="n">
@@ -3977,7 +4582,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n">
+      <c r="C123" s="8" t="n">
         <v>23.15</v>
       </c>
       <c r="D123" t="n">
@@ -4005,7 +4610,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n">
+      <c r="C124" s="8" t="n">
         <v>55.02</v>
       </c>
       <c r="D124" t="n">
@@ -4033,7 +4638,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
+      <c r="C125" s="8" t="n">
         <v>20.59</v>
       </c>
       <c r="D125" t="n">
@@ -4061,7 +4666,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
+      <c r="C126" s="8" t="n">
         <v>41.82</v>
       </c>
       <c r="D126" t="n">
@@ -4089,7 +4694,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
+      <c r="C127" s="8" t="n">
         <v>36</v>
       </c>
       <c r="D127" t="n">
@@ -4117,7 +4722,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n">
+      <c r="C128" s="8" t="n">
         <v>27.37</v>
       </c>
       <c r="D128" t="n">
@@ -4145,7 +4750,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n">
+      <c r="C129" s="8" t="n">
         <v>52.72</v>
       </c>
       <c r="D129" t="n">
@@ -4173,7 +4778,7 @@
           <t>Default</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n">
+      <c r="C130" s="8" t="n">
         <v>41.6</v>
       </c>
       <c r="D130" t="n">
@@ -4201,7 +4806,7 @@
           <t>Erotica</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n">
+      <c r="C131" s="8" t="n">
         <v>19.19</v>
       </c>
       <c r="D131" t="n">
@@ -4229,7 +4834,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n">
+      <c r="C132" s="8" t="n">
         <v>52.37</v>
       </c>
       <c r="D132" t="n">
@@ -4257,7 +4862,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n">
+      <c r="C133" s="8" t="n">
         <v>56.63</v>
       </c>
       <c r="D133" t="n">
@@ -4285,7 +4890,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n">
+      <c r="C134" s="8" t="n">
         <v>28.09</v>
       </c>
       <c r="D134" t="n">
@@ -4313,7 +4918,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n">
+      <c r="C135" s="8" t="n">
         <v>56.02</v>
       </c>
       <c r="D135" t="n">
@@ -4341,7 +4946,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n">
+      <c r="C136" s="8" t="n">
         <v>43.29</v>
       </c>
       <c r="D136" t="n">
@@ -4369,7 +4974,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n">
+      <c r="C137" s="8" t="n">
         <v>37.51</v>
       </c>
       <c r="D137" t="n">
@@ -4397,7 +5002,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C138" s="2" t="n">
+      <c r="C138" s="8" t="n">
         <v>42.98</v>
       </c>
       <c r="D138" t="n">
@@ -4425,7 +5030,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C139" s="2" t="n">
+      <c r="C139" s="8" t="n">
         <v>29.65</v>
       </c>
       <c r="D139" t="n">
@@ -4453,7 +5058,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C140" s="2" t="n">
+      <c r="C140" s="8" t="n">
         <v>39.61</v>
       </c>
       <c r="D140" t="n">
@@ -4481,7 +5086,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n">
+      <c r="C141" s="8" t="n">
         <v>56.4</v>
       </c>
       <c r="D141" t="n">
@@ -4509,7 +5114,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n">
+      <c r="C142" s="8" t="n">
         <v>13.34</v>
       </c>
       <c r="D142" t="n">
@@ -4537,7 +5142,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C143" s="2" t="n">
+      <c r="C143" s="8" t="n">
         <v>25.02</v>
       </c>
       <c r="D143" t="n">
@@ -4565,7 +5170,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n">
+      <c r="C144" s="8" t="n">
         <v>38.73</v>
       </c>
       <c r="D144" t="n">
@@ -4593,7 +5198,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n">
+      <c r="C145" s="8" t="n">
         <v>44.73</v>
       </c>
       <c r="D145" t="n">
@@ -4621,7 +5226,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C146" s="2" t="n">
+      <c r="C146" s="8" t="n">
         <v>44.28</v>
       </c>
       <c r="D146" t="n">
@@ -4649,7 +5254,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n">
+      <c r="C147" s="8" t="n">
         <v>52.26</v>
       </c>
       <c r="D147" t="n">
@@ -4677,7 +5282,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n">
+      <c r="C148" s="8" t="n">
         <v>46.02</v>
       </c>
       <c r="D148" t="n">
@@ -4705,7 +5310,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C149" s="2" t="n">
+      <c r="C149" s="8" t="n">
         <v>32.3</v>
       </c>
       <c r="D149" t="n">
@@ -4733,7 +5338,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C150" s="2" t="n">
+      <c r="C150" s="8" t="n">
         <v>35.07</v>
       </c>
       <c r="D150" t="n">
@@ -4761,7 +5366,7 @@
           <t>Fantasy</t>
         </is>
       </c>
-      <c r="C151" s="2" t="n">
+      <c r="C151" s="8" t="n">
         <v>18.78</v>
       </c>
       <c r="D151" t="n">
@@ -4789,7 +5394,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C152" s="2" t="n">
+      <c r="C152" s="8" t="n">
         <v>27.09</v>
       </c>
       <c r="D152" t="n">
@@ -4817,7 +5422,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C153" s="2" t="n">
+      <c r="C153" s="8" t="n">
         <v>53.53</v>
       </c>
       <c r="D153" t="n">
@@ -4845,7 +5450,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C154" s="2" t="n">
+      <c r="C154" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="D154" t="n">
@@ -4873,7 +5478,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C155" s="2" t="n">
+      <c r="C155" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="D155" t="n">
@@ -4901,7 +5506,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C156" s="2" t="n">
+      <c r="C156" s="8" t="n">
         <v>24.48</v>
       </c>
       <c r="D156" t="n">
@@ -4929,7 +5534,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C157" s="2" t="n">
+      <c r="C157" s="8" t="n">
         <v>41.56</v>
       </c>
       <c r="D157" t="n">
@@ -4957,7 +5562,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C158" s="2" t="n">
+      <c r="C158" s="8" t="n">
         <v>47.61</v>
       </c>
       <c r="D158" t="n">
@@ -4985,7 +5590,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C159" s="2" t="n">
+      <c r="C159" s="8" t="n">
         <v>55.84</v>
       </c>
       <c r="D159" t="n">
@@ -5013,7 +5618,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C160" s="2" t="n">
+      <c r="C160" s="8" t="n">
         <v>50.1</v>
       </c>
       <c r="D160" t="n">
@@ -5041,7 +5646,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C161" s="2" t="n">
+      <c r="C161" s="8" t="n">
         <v>26.41</v>
       </c>
       <c r="D161" t="n">
@@ -5069,7 +5674,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C162" s="2" t="n">
+      <c r="C162" s="8" t="n">
         <v>45.21</v>
       </c>
       <c r="D162" t="n">
@@ -5097,7 +5702,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C163" s="2" t="n">
+      <c r="C163" s="8" t="n">
         <v>25.85</v>
       </c>
       <c r="D163" t="n">
@@ -5125,7 +5730,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C164" s="2" t="n">
+      <c r="C164" s="8" t="n">
         <v>54.11</v>
       </c>
       <c r="D164" t="n">
@@ -5153,7 +5758,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C165" s="2" t="n">
+      <c r="C165" s="8" t="n">
         <v>51.36</v>
       </c>
       <c r="D165" t="n">
@@ -5181,7 +5786,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C166" s="2" t="n">
+      <c r="C166" s="8" t="n">
         <v>52.67</v>
       </c>
       <c r="D166" t="n">
@@ -5209,7 +5814,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C167" s="2" t="n">
+      <c r="C167" s="8" t="n">
         <v>27.88</v>
       </c>
       <c r="D167" t="n">
@@ -5237,7 +5842,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C168" s="2" t="n">
+      <c r="C168" s="8" t="n">
         <v>42.15</v>
       </c>
       <c r="D168" t="n">
@@ -5265,7 +5870,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C169" s="2" t="n">
+      <c r="C169" s="8" t="n">
         <v>17.27</v>
       </c>
       <c r="D169" t="n">
@@ -5293,7 +5898,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C170" s="2" t="n">
+      <c r="C170" s="8" t="n">
         <v>21.04</v>
       </c>
       <c r="D170" t="n">
@@ -5321,7 +5926,7 @@
           <t>Fiction</t>
         </is>
       </c>
-      <c r="C171" s="2" t="n">
+      <c r="C171" s="8" t="n">
         <v>50.27</v>
       </c>
       <c r="D171" t="n">
@@ -5349,7 +5954,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C172" s="2" t="n">
+      <c r="C172" s="8" t="n">
         <v>53.63</v>
       </c>
       <c r="D172" t="n">
@@ -5377,7 +5982,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C173" s="2" t="n">
+      <c r="C173" s="8" t="n">
         <v>38.77</v>
       </c>
       <c r="D173" t="n">
@@ -5405,7 +6010,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C174" s="2" t="n">
+      <c r="C174" s="8" t="n">
         <v>28.01</v>
       </c>
       <c r="D174" t="n">
@@ -5433,7 +6038,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C175" s="2" t="n">
+      <c r="C175" s="8" t="n">
         <v>50.62</v>
       </c>
       <c r="D175" t="n">
@@ -5461,7 +6066,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C176" s="2" t="n">
+      <c r="C176" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="D176" t="n">
@@ -5489,7 +6094,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C177" s="2" t="n">
+      <c r="C177" s="8" t="n">
         <v>42.16</v>
       </c>
       <c r="D177" t="n">
@@ -5517,7 +6122,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C178" s="2" t="n">
+      <c r="C178" s="8" t="n">
         <v>20.1</v>
       </c>
       <c r="D178" t="n">
@@ -5545,7 +6150,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C179" s="2" t="n">
+      <c r="C179" s="8" t="n">
         <v>30.52</v>
       </c>
       <c r="D179" t="n">
@@ -5573,7 +6178,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C180" s="2" t="n">
+      <c r="C180" s="8" t="n">
         <v>19.55</v>
       </c>
       <c r="D180" t="n">
@@ -5601,7 +6206,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C181" s="2" t="n">
+      <c r="C181" s="8" t="n">
         <v>40.11</v>
       </c>
       <c r="D181" t="n">
@@ -5629,7 +6234,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C182" s="2" t="n">
+      <c r="C182" s="8" t="n">
         <v>14.02</v>
       </c>
       <c r="D182" t="n">
@@ -5657,7 +6262,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C183" s="2" t="n">
+      <c r="C183" s="8" t="n">
         <v>11.53</v>
       </c>
       <c r="D183" t="n">
@@ -5685,7 +6290,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C184" s="2" t="n">
+      <c r="C184" s="8" t="n">
         <v>33.37</v>
       </c>
       <c r="D184" t="n">
@@ -5713,7 +6318,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C185" s="2" t="n">
+      <c r="C185" s="8" t="n">
         <v>11.38</v>
       </c>
       <c r="D185" t="n">
@@ -5741,7 +6346,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C186" s="2" t="n">
+      <c r="C186" s="8" t="n">
         <v>41.25</v>
       </c>
       <c r="D186" t="n">
@@ -5769,7 +6374,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C187" s="2" t="n">
+      <c r="C187" s="8" t="n">
         <v>28.77</v>
       </c>
       <c r="D187" t="n">
@@ -5797,7 +6402,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C188" s="2" t="n">
+      <c r="C188" s="8" t="n">
         <v>37.6</v>
       </c>
       <c r="D188" t="n">
@@ -5825,7 +6430,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C189" s="2" t="n">
+      <c r="C189" s="8" t="n">
         <v>12.34</v>
       </c>
       <c r="D189" t="n">
@@ -5853,7 +6458,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C190" s="2" t="n">
+      <c r="C190" s="8" t="n">
         <v>37.34</v>
       </c>
       <c r="D190" t="n">
@@ -5881,7 +6486,7 @@
           <t>Food and Drink</t>
         </is>
       </c>
-      <c r="C191" s="2" t="n">
+      <c r="C191" s="8" t="n">
         <v>56.41</v>
       </c>
       <c r="D191" t="n">
@@ -5909,7 +6514,7 @@
           <t>Health</t>
         </is>
       </c>
-      <c r="C192" s="2" t="n">
+      <c r="C192" s="8" t="n">
         <v>49.71</v>
       </c>
       <c r="D192" t="n">
@@ -5937,7 +6542,7 @@
           <t>Health</t>
         </is>
       </c>
-      <c r="C193" s="2" t="n">
+      <c r="C193" s="8" t="n">
         <v>54.07</v>
       </c>
       <c r="D193" t="n">
@@ -5965,7 +6570,7 @@
           <t>Health</t>
         </is>
       </c>
-      <c r="C194" s="2" t="n">
+      <c r="C194" s="8" t="n">
         <v>52.98</v>
       </c>
       <c r="D194" t="n">
@@ -5993,7 +6598,7 @@
           <t>Health</t>
         </is>
       </c>
-      <c r="C195" s="2" t="n">
+      <c r="C195" s="8" t="n">
         <v>49.05</v>
       </c>
       <c r="D195" t="n">
@@ -6021,7 +6626,7 @@
           <t>Historical</t>
         </is>
       </c>
-      <c r="C196" s="2" t="n">
+      <c r="C196" s="8" t="n">
         <v>29.87</v>
       </c>
       <c r="D196" t="n">
@@ -6049,7 +6654,7 @@
           <t>Historical</t>
         </is>
       </c>
-      <c r="C197" s="2" t="n">
+      <c r="C197" s="8" t="n">
         <v>15.79</v>
       </c>
       <c r="D197" t="n">
@@ -6077,7 +6682,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C198" s="2" t="n">
+      <c r="C198" s="8" t="n">
         <v>55.53</v>
       </c>
       <c r="D198" t="n">
@@ -6105,7 +6710,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C199" s="2" t="n">
+      <c r="C199" s="8" t="n">
         <v>39.01</v>
       </c>
       <c r="D199" t="n">
@@ -6133,7 +6738,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C200" s="2" t="n">
+      <c r="C200" s="8" t="n">
         <v>29.69</v>
       </c>
       <c r="D200" t="n">
@@ -6161,7 +6766,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C201" s="2" t="n">
+      <c r="C201" s="8" t="n">
         <v>26.77</v>
       </c>
       <c r="D201" t="n">
@@ -6189,7 +6794,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C202" s="2" t="n">
+      <c r="C202" s="8" t="n">
         <v>46.83</v>
       </c>
       <c r="D202" t="n">
@@ -6217,7 +6822,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C203" s="2" t="n">
+      <c r="C203" s="8" t="n">
         <v>45.84</v>
       </c>
       <c r="D203" t="n">
@@ -6245,7 +6850,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C204" s="2" t="n">
+      <c r="C204" s="8" t="n">
         <v>17.28</v>
       </c>
       <c r="D204" t="n">
@@ -6273,7 +6878,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C205" s="2" t="n">
+      <c r="C205" s="8" t="n">
         <v>20.55</v>
       </c>
       <c r="D205" t="n">
@@ -6301,7 +6906,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C206" s="2" t="n">
+      <c r="C206" s="8" t="n">
         <v>30.25</v>
       </c>
       <c r="D206" t="n">
@@ -6329,7 +6934,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C207" s="2" t="n">
+      <c r="C207" s="8" t="n">
         <v>16.62</v>
       </c>
       <c r="D207" t="n">
@@ -6357,7 +6962,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C208" s="2" t="n">
+      <c r="C208" s="8" t="n">
         <v>49.53</v>
       </c>
       <c r="D208" t="n">
@@ -6385,7 +6990,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C209" s="2" t="n">
+      <c r="C209" s="8" t="n">
         <v>36.95</v>
       </c>
       <c r="D209" t="n">
@@ -6413,7 +7018,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C210" s="2" t="n">
+      <c r="C210" s="8" t="n">
         <v>37.34</v>
       </c>
       <c r="D210" t="n">
@@ -6441,7 +7046,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C211" s="2" t="n">
+      <c r="C211" s="8" t="n">
         <v>55.55</v>
       </c>
       <c r="D211" t="n">
@@ -6469,7 +7074,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C212" s="2" t="n">
+      <c r="C212" s="8" t="n">
         <v>28.08</v>
       </c>
       <c r="D212" t="n">
@@ -6497,7 +7102,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C213" s="2" t="n">
+      <c r="C213" s="8" t="n">
         <v>28.32</v>
       </c>
       <c r="D213" t="n">
@@ -6525,7 +7130,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C214" s="2" t="n">
+      <c r="C214" s="8" t="n">
         <v>35.66</v>
       </c>
       <c r="D214" t="n">
@@ -6553,7 +7158,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C215" s="2" t="n">
+      <c r="C215" s="8" t="n">
         <v>53.74</v>
       </c>
       <c r="D215" t="n">
@@ -6581,7 +7186,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C216" s="2" t="n">
+      <c r="C216" s="8" t="n">
         <v>21.07</v>
       </c>
       <c r="D216" t="n">
@@ -6609,7 +7214,7 @@
           <t>Historical Fiction</t>
         </is>
       </c>
-      <c r="C217" s="2" t="n">
+      <c r="C217" s="8" t="n">
         <v>32.97</v>
       </c>
       <c r="D217" t="n">
@@ -6637,7 +7242,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C218" s="2" t="n">
+      <c r="C218" s="8" t="n">
         <v>44.48</v>
       </c>
       <c r="D218" t="n">
@@ -6665,7 +7270,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C219" s="2" t="n">
+      <c r="C219" s="8" t="n">
         <v>21.8</v>
       </c>
       <c r="D219" t="n">
@@ -6693,7 +7298,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C220" s="2" t="n">
+      <c r="C220" s="8" t="n">
         <v>14.58</v>
       </c>
       <c r="D220" t="n">
@@ -6721,7 +7326,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C221" s="2" t="n">
+      <c r="C221" s="8" t="n">
         <v>52.4</v>
       </c>
       <c r="D221" t="n">
@@ -6749,7 +7354,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C222" s="2" t="n">
+      <c r="C222" s="8" t="n">
         <v>51.22</v>
       </c>
       <c r="D222" t="n">
@@ -6777,7 +7382,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C223" s="2" t="n">
+      <c r="C223" s="8" t="n">
         <v>11.45</v>
       </c>
       <c r="D223" t="n">
@@ -6805,7 +7410,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C224" s="2" t="n">
+      <c r="C224" s="8" t="n">
         <v>58.55</v>
       </c>
       <c r="D224" t="n">
@@ -6833,7 +7438,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C225" s="2" t="n">
+      <c r="C225" s="8" t="n">
         <v>43.7</v>
       </c>
       <c r="D225" t="n">
@@ -6861,7 +7466,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C226" s="2" t="n">
+      <c r="C226" s="8" t="n">
         <v>36.28</v>
       </c>
       <c r="D226" t="n">
@@ -6889,7 +7494,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C227" s="2" t="n">
+      <c r="C227" s="8" t="n">
         <v>54.23</v>
       </c>
       <c r="D227" t="n">
@@ -6917,7 +7522,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C228" s="2" t="n">
+      <c r="C228" s="8" t="n">
         <v>19.73</v>
       </c>
       <c r="D228" t="n">
@@ -6945,7 +7550,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C229" s="2" t="n">
+      <c r="C229" s="8" t="n">
         <v>14.54</v>
       </c>
       <c r="D229" t="n">
@@ -6973,7 +7578,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C230" s="2" t="n">
+      <c r="C230" s="8" t="n">
         <v>55.91</v>
       </c>
       <c r="D230" t="n">
@@ -7001,7 +7606,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C231" s="2" t="n">
+      <c r="C231" s="8" t="n">
         <v>42.91</v>
       </c>
       <c r="D231" t="n">
@@ -7029,7 +7634,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C232" s="2" t="n">
+      <c r="C232" s="8" t="n">
         <v>39.67</v>
       </c>
       <c r="D232" t="n">
@@ -7057,7 +7662,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C233" s="2" t="n">
+      <c r="C233" s="8" t="n">
         <v>59.64</v>
       </c>
       <c r="D233" t="n">
@@ -7085,7 +7690,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C234" s="2" t="n">
+      <c r="C234" s="8" t="n">
         <v>25.52</v>
       </c>
       <c r="D234" t="n">
@@ -7113,7 +7718,7 @@
           <t>History</t>
         </is>
       </c>
-      <c r="C235" s="2" t="n">
+      <c r="C235" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="D235" t="n">
@@ -7141,7 +7746,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C236" s="2" t="n">
+      <c r="C236" s="8" t="n">
         <v>49.56</v>
       </c>
       <c r="D236" t="n">
@@ -7169,7 +7774,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C237" s="2" t="n">
+      <c r="C237" s="8" t="n">
         <v>48.64</v>
       </c>
       <c r="D237" t="n">
@@ -7197,7 +7802,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C238" s="2" t="n">
+      <c r="C238" s="8" t="n">
         <v>40.12</v>
       </c>
       <c r="D238" t="n">
@@ -7225,7 +7830,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C239" s="2" t="n">
+      <c r="C239" s="8" t="n">
         <v>35.63</v>
       </c>
       <c r="D239" t="n">
@@ -7253,7 +7858,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C240" s="2" t="n">
+      <c r="C240" s="8" t="n">
         <v>21.36</v>
       </c>
       <c r="D240" t="n">
@@ -7281,7 +7886,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C241" s="2" t="n">
+      <c r="C241" s="8" t="n">
         <v>54.89</v>
       </c>
       <c r="D241" t="n">
@@ -7309,7 +7914,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C242" s="2" t="n">
+      <c r="C242" s="8" t="n">
         <v>25.01</v>
       </c>
       <c r="D242" t="n">
@@ -7337,7 +7942,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C243" s="2" t="n">
+      <c r="C243" s="8" t="n">
         <v>34.79</v>
       </c>
       <c r="D243" t="n">
@@ -7365,7 +7970,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C244" s="2" t="n">
+      <c r="C244" s="8" t="n">
         <v>47.51</v>
       </c>
       <c r="D244" t="n">
@@ -7393,7 +7998,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C245" s="2" t="n">
+      <c r="C245" s="8" t="n">
         <v>12.75</v>
       </c>
       <c r="D245" t="n">
@@ -7421,7 +8026,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C246" s="2" t="n">
+      <c r="C246" s="8" t="n">
         <v>10.56</v>
       </c>
       <c r="D246" t="n">
@@ -7449,7 +8054,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C247" s="2" t="n">
+      <c r="C247" s="8" t="n">
         <v>36.97</v>
       </c>
       <c r="D247" t="n">
@@ -7477,7 +8082,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C248" s="2" t="n">
+      <c r="C248" s="8" t="n">
         <v>23.37</v>
       </c>
       <c r="D248" t="n">
@@ -7505,7 +8110,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C249" s="2" t="n">
+      <c r="C249" s="8" t="n">
         <v>39.25</v>
       </c>
       <c r="D249" t="n">
@@ -7533,7 +8138,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C250" s="2" t="n">
+      <c r="C250" s="8" t="n">
         <v>49.47</v>
       </c>
       <c r="D250" t="n">
@@ -7561,7 +8166,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C251" s="2" t="n">
+      <c r="C251" s="8" t="n">
         <v>23.4</v>
       </c>
       <c r="D251" t="n">
@@ -7589,7 +8194,7 @@
           <t>Horror</t>
         </is>
       </c>
-      <c r="C252" s="2" t="n">
+      <c r="C252" s="8" t="n">
         <v>57.86</v>
       </c>
       <c r="D252" t="n">
@@ -7617,7 +8222,7 @@
           <t>Humor</t>
         </is>
       </c>
-      <c r="C253" s="2" t="n">
+      <c r="C253" s="8" t="n">
         <v>43.68</v>
       </c>
       <c r="D253" t="n">
@@ -7645,7 +8250,7 @@
           <t>Humor</t>
         </is>
       </c>
-      <c r="C254" s="2" t="n">
+      <c r="C254" s="8" t="n">
         <v>51.07</v>
       </c>
       <c r="D254" t="n">
@@ -7673,7 +8278,7 @@
           <t>Humor</t>
         </is>
       </c>
-      <c r="C255" s="2" t="n">
+      <c r="C255" s="8" t="n">
         <v>14.75</v>
       </c>
       <c r="D255" t="n">
@@ -7701,7 +8306,7 @@
           <t>Humor</t>
         </is>
       </c>
-      <c r="C256" s="2" t="n">
+      <c r="C256" s="8" t="n">
         <v>25.98</v>
       </c>
       <c r="D256" t="n">
@@ -7729,7 +8334,7 @@
           <t>Humor</t>
         </is>
       </c>
-      <c r="C257" s="2" t="n">
+      <c r="C257" s="8" t="n">
         <v>55.5</v>
       </c>
       <c r="D257" t="n">
@@ -7757,7 +8362,7 @@
           <t>Humor</t>
         </is>
       </c>
-      <c r="C258" s="2" t="n">
+      <c r="C258" s="8" t="n">
         <v>31.69</v>
       </c>
       <c r="D258" t="n">
@@ -7785,7 +8390,7 @@
           <t>Humor</t>
         </is>
       </c>
-      <c r="C259" s="2" t="n">
+      <c r="C259" s="8" t="n">
         <v>11.83</v>
       </c>
       <c r="D259" t="n">
@@ -7813,7 +8418,7 @@
           <t>Humor</t>
         </is>
       </c>
-      <c r="C260" s="2" t="n">
+      <c r="C260" s="8" t="n">
         <v>44.07</v>
       </c>
       <c r="D260" t="n">
@@ -7841,7 +8446,7 @@
           <t>Humor</t>
         </is>
       </c>
-      <c r="C261" s="2" t="n">
+      <c r="C261" s="8" t="n">
         <v>25.55</v>
       </c>
       <c r="D261" t="n">
@@ -7869,7 +8474,7 @@
           <t>Humor</t>
         </is>
       </c>
-      <c r="C262" s="2" t="n">
+      <c r="C262" s="8" t="n">
         <v>30.89</v>
       </c>
       <c r="D262" t="n">
@@ -7897,7 +8502,7 @@
           <t>Music</t>
         </is>
       </c>
-      <c r="C263" s="2" t="n">
+      <c r="C263" s="8" t="n">
         <v>52.6</v>
       </c>
       <c r="D263" t="n">
@@ -7925,7 +8530,7 @@
           <t>Music</t>
         </is>
       </c>
-      <c r="C264" s="2" t="n">
+      <c r="C264" s="8" t="n">
         <v>28.8</v>
       </c>
       <c r="D264" t="n">
@@ -7953,7 +8558,7 @@
           <t>Music</t>
         </is>
       </c>
-      <c r="C265" s="2" t="n">
+      <c r="C265" s="8" t="n">
         <v>37.32</v>
       </c>
       <c r="D265" t="n">
@@ -7981,7 +8586,7 @@
           <t>Music</t>
         </is>
       </c>
-      <c r="C266" s="2" t="n">
+      <c r="C266" s="8" t="n">
         <v>45.05</v>
       </c>
       <c r="D266" t="n">
@@ -8009,7 +8614,7 @@
           <t>Music</t>
         </is>
       </c>
-      <c r="C267" s="2" t="n">
+      <c r="C267" s="8" t="n">
         <v>31.58</v>
       </c>
       <c r="D267" t="n">
@@ -8037,7 +8642,7 @@
           <t>Music</t>
         </is>
       </c>
-      <c r="C268" s="2" t="n">
+      <c r="C268" s="8" t="n">
         <v>18.03</v>
       </c>
       <c r="D268" t="n">
@@ -8065,7 +8670,7 @@
           <t>Music</t>
         </is>
       </c>
-      <c r="C269" s="2" t="n">
+      <c r="C269" s="8" t="n">
         <v>20.02</v>
       </c>
       <c r="D269" t="n">
@@ -8093,7 +8698,7 @@
           <t>Music</t>
         </is>
       </c>
-      <c r="C270" s="2" t="n">
+      <c r="C270" s="8" t="n">
         <v>55.66</v>
       </c>
       <c r="D270" t="n">
@@ -8121,7 +8726,7 @@
           <t>Music</t>
         </is>
       </c>
-      <c r="C271" s="2" t="n">
+      <c r="C271" s="8" t="n">
         <v>12.36</v>
       </c>
       <c r="D271" t="n">
@@ -8149,7 +8754,7 @@
           <t>Music</t>
         </is>
       </c>
-      <c r="C272" s="2" t="n">
+      <c r="C272" s="8" t="n">
         <v>57.25</v>
       </c>
       <c r="D272" t="n">
@@ -8177,7 +8782,7 @@
           <t>Music</t>
         </is>
       </c>
-      <c r="C273" s="2" t="n">
+      <c r="C273" s="8" t="n">
         <v>31.19</v>
       </c>
       <c r="D273" t="n">
@@ -8205,7 +8810,7 @@
           <t>Music</t>
         </is>
       </c>
-      <c r="C274" s="2" t="n">
+      <c r="C274" s="8" t="n">
         <v>35.02</v>
       </c>
       <c r="D274" t="n">
@@ -8233,7 +8838,7 @@
           <t>Music</t>
         </is>
       </c>
-      <c r="C275" s="2" t="n">
+      <c r="C275" s="8" t="n">
         <v>38.4</v>
       </c>
       <c r="D275" t="n">
@@ -8261,7 +8866,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C276" s="2" t="n">
+      <c r="C276" s="8" t="n">
         <v>16.64</v>
       </c>
       <c r="D276" t="n">
@@ -8289,7 +8894,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C277" s="2" t="n">
+      <c r="C277" s="8" t="n">
         <v>16.73</v>
       </c>
       <c r="D277" t="n">
@@ -8317,7 +8922,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C278" s="2" t="n">
+      <c r="C278" s="8" t="n">
         <v>48.35</v>
       </c>
       <c r="D278" t="n">
@@ -8345,7 +8950,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C279" s="2" t="n">
+      <c r="C279" s="8" t="n">
         <v>59.48</v>
       </c>
       <c r="D279" t="n">
@@ -8373,7 +8978,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C280" s="2" t="n">
+      <c r="C280" s="8" t="n">
         <v>20.89</v>
       </c>
       <c r="D280" t="n">
@@ -8401,7 +9006,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C281" s="2" t="n">
+      <c r="C281" s="8" t="n">
         <v>11.84</v>
       </c>
       <c r="D281" t="n">
@@ -8429,7 +9034,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C282" s="2" t="n">
+      <c r="C282" s="8" t="n">
         <v>19.63</v>
       </c>
       <c r="D282" t="n">
@@ -8457,7 +9062,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C283" s="2" t="n">
+      <c r="C283" s="8" t="n">
         <v>35.28</v>
       </c>
       <c r="D283" t="n">
@@ -8485,7 +9090,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C284" s="2" t="n">
+      <c r="C284" s="8" t="n">
         <v>54.36</v>
       </c>
       <c r="D284" t="n">
@@ -8513,7 +9118,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C285" s="2" t="n">
+      <c r="C285" s="8" t="n">
         <v>13.71</v>
       </c>
       <c r="D285" t="n">
@@ -8541,7 +9146,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C286" s="2" t="n">
+      <c r="C286" s="8" t="n">
         <v>26.8</v>
       </c>
       <c r="D286" t="n">
@@ -8569,7 +9174,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C287" s="2" t="n">
+      <c r="C287" s="8" t="n">
         <v>47.82</v>
       </c>
       <c r="D287" t="n">
@@ -8597,7 +9202,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C288" s="2" t="n">
+      <c r="C288" s="8" t="n">
         <v>10.69</v>
       </c>
       <c r="D288" t="n">
@@ -8625,7 +9230,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C289" s="2" t="n">
+      <c r="C289" s="8" t="n">
         <v>13.92</v>
       </c>
       <c r="D289" t="n">
@@ -8653,7 +9258,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C290" s="2" t="n">
+      <c r="C290" s="8" t="n">
         <v>52.3</v>
       </c>
       <c r="D290" t="n">
@@ -8681,7 +9286,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C291" s="2" t="n">
+      <c r="C291" s="8" t="n">
         <v>54.21</v>
       </c>
       <c r="D291" t="n">
@@ -8709,7 +9314,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C292" s="2" t="n">
+      <c r="C292" s="8" t="n">
         <v>44.1</v>
       </c>
       <c r="D292" t="n">
@@ -8737,7 +9342,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C293" s="2" t="n">
+      <c r="C293" s="8" t="n">
         <v>56.5</v>
       </c>
       <c r="D293" t="n">
@@ -8765,7 +9370,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C294" s="2" t="n">
+      <c r="C294" s="8" t="n">
         <v>27.26</v>
       </c>
       <c r="D294" t="n">
@@ -8793,7 +9398,7 @@
           <t>Mystery</t>
         </is>
       </c>
-      <c r="C295" s="2" t="n">
+      <c r="C295" s="8" t="n">
         <v>25.37</v>
       </c>
       <c r="D295" t="n">
@@ -8821,7 +9426,7 @@
           <t>New Adult</t>
         </is>
       </c>
-      <c r="C296" s="2" t="n">
+      <c r="C296" s="8" t="n">
         <v>39.45</v>
       </c>
       <c r="D296" t="n">
@@ -8849,7 +9454,7 @@
           <t>New Adult</t>
         </is>
       </c>
-      <c r="C297" s="2" t="n">
+      <c r="C297" s="8" t="n">
         <v>58.35</v>
       </c>
       <c r="D297" t="n">
@@ -8877,7 +9482,7 @@
           <t>New Adult</t>
         </is>
       </c>
-      <c r="C298" s="2" t="n">
+      <c r="C298" s="8" t="n">
         <v>36.29</v>
       </c>
       <c r="D298" t="n">
@@ -8905,7 +9510,7 @@
           <t>New Adult</t>
         </is>
       </c>
-      <c r="C299" s="2" t="n">
+      <c r="C299" s="8" t="n">
         <v>55.85</v>
       </c>
       <c r="D299" t="n">
@@ -8933,7 +9538,7 @@
           <t>New Adult</t>
         </is>
       </c>
-      <c r="C300" s="2" t="n">
+      <c r="C300" s="8" t="n">
         <v>43.29</v>
       </c>
       <c r="D300" t="n">
@@ -8961,7 +9566,7 @@
           <t>New Adult</t>
         </is>
       </c>
-      <c r="C301" s="2" t="n">
+      <c r="C301" s="8" t="n">
         <v>45.07</v>
       </c>
       <c r="D301" t="n">
@@ -8989,7 +9594,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C302" s="2" t="n">
+      <c r="C302" s="8" t="n">
         <v>23.11</v>
       </c>
       <c r="D302" t="n">
@@ -9017,7 +9622,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C303" s="2" t="n">
+      <c r="C303" s="8" t="n">
         <v>30.81</v>
       </c>
       <c r="D303" t="n">
@@ -9045,7 +9650,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C304" s="2" t="n">
+      <c r="C304" s="8" t="n">
         <v>29.14</v>
       </c>
       <c r="D304" t="n">
@@ -9073,7 +9678,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C305" s="2" t="n">
+      <c r="C305" s="8" t="n">
         <v>54.35</v>
       </c>
       <c r="D305" t="n">
@@ -9101,7 +9706,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C306" s="2" t="n">
+      <c r="C306" s="8" t="n">
         <v>22</v>
       </c>
       <c r="D306" t="n">
@@ -9129,7 +9734,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C307" s="2" t="n">
+      <c r="C307" s="8" t="n">
         <v>26.41</v>
       </c>
       <c r="D307" t="n">
@@ -9157,7 +9762,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C308" s="2" t="n">
+      <c r="C308" s="8" t="n">
         <v>19.83</v>
       </c>
       <c r="D308" t="n">
@@ -9185,7 +9790,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C309" s="2" t="n">
+      <c r="C309" s="8" t="n">
         <v>12.23</v>
       </c>
       <c r="D309" t="n">
@@ -9213,7 +9818,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C310" s="2" t="n">
+      <c r="C310" s="8" t="n">
         <v>41.83</v>
       </c>
       <c r="D310" t="n">
@@ -9241,7 +9846,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C311" s="2" t="n">
+      <c r="C311" s="8" t="n">
         <v>38.49</v>
       </c>
       <c r="D311" t="n">
@@ -9269,7 +9874,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C312" s="2" t="n">
+      <c r="C312" s="8" t="n">
         <v>56.06</v>
       </c>
       <c r="D312" t="n">
@@ -9297,7 +9902,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C313" s="2" t="n">
+      <c r="C313" s="8" t="n">
         <v>31.05</v>
       </c>
       <c r="D313" t="n">
@@ -9325,7 +9930,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C314" s="2" t="n">
+      <c r="C314" s="8" t="n">
         <v>17.24</v>
       </c>
       <c r="D314" t="n">
@@ -9353,7 +9958,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C315" s="2" t="n">
+      <c r="C315" s="8" t="n">
         <v>37.13</v>
       </c>
       <c r="D315" t="n">
@@ -9381,7 +9986,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C316" s="2" t="n">
+      <c r="C316" s="8" t="n">
         <v>16.77</v>
       </c>
       <c r="D316" t="n">
@@ -9409,7 +10014,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C317" s="2" t="n">
+      <c r="C317" s="8" t="n">
         <v>38.21</v>
       </c>
       <c r="D317" t="n">
@@ -9437,7 +10042,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C318" s="2" t="n">
+      <c r="C318" s="8" t="n">
         <v>43.54</v>
       </c>
       <c r="D318" t="n">
@@ -9465,7 +10070,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C319" s="2" t="n">
+      <c r="C319" s="8" t="n">
         <v>31.12</v>
       </c>
       <c r="D319" t="n">
@@ -9493,7 +10098,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C320" s="2" t="n">
+      <c r="C320" s="8" t="n">
         <v>44.18</v>
       </c>
       <c r="D320" t="n">
@@ -9521,7 +10126,7 @@
           <t>Nonfiction</t>
         </is>
       </c>
-      <c r="C321" s="2" t="n">
+      <c r="C321" s="8" t="n">
         <v>40.3</v>
       </c>
       <c r="D321" t="n">
@@ -9549,7 +10154,7 @@
           <t>Novels</t>
         </is>
       </c>
-      <c r="C322" s="2" t="n">
+      <c r="C322" s="8" t="n">
         <v>54.81</v>
       </c>
       <c r="D322" t="n">
@@ -9577,7 +10182,7 @@
           <t>Paranormal</t>
         </is>
       </c>
-      <c r="C323" s="2" t="n">
+      <c r="C323" s="8" t="n">
         <v>15.4</v>
       </c>
       <c r="D323" t="n">
@@ -9605,7 +10210,7 @@
           <t>Parenting</t>
         </is>
       </c>
-      <c r="C324" s="2" t="n">
+      <c r="C324" s="8" t="n">
         <v>37.35</v>
       </c>
       <c r="D324" t="n">
@@ -9633,7 +10238,7 @@
           <t>Philosophy</t>
         </is>
       </c>
-      <c r="C325" s="2" t="n">
+      <c r="C325" s="8" t="n">
         <v>29.93</v>
       </c>
       <c r="D325" t="n">
@@ -9661,7 +10266,7 @@
           <t>Philosophy</t>
         </is>
       </c>
-      <c r="C326" s="2" t="n">
+      <c r="C326" s="8" t="n">
         <v>43.38</v>
       </c>
       <c r="D326" t="n">
@@ -9689,7 +10294,7 @@
           <t>Philosophy</t>
         </is>
       </c>
-      <c r="C327" s="2" t="n">
+      <c r="C327" s="8" t="n">
         <v>20.75</v>
       </c>
       <c r="D327" t="n">
@@ -9717,7 +10322,7 @@
           <t>Philosophy</t>
         </is>
       </c>
-      <c r="C328" s="2" t="n">
+      <c r="C328" s="8" t="n">
         <v>47.13</v>
       </c>
       <c r="D328" t="n">
@@ -9745,7 +10350,7 @@
           <t>Philosophy</t>
         </is>
       </c>
-      <c r="C329" s="2" t="n">
+      <c r="C329" s="8" t="n">
         <v>25.89</v>
       </c>
       <c r="D329" t="n">
@@ -9773,7 +10378,7 @@
           <t>Philosophy</t>
         </is>
       </c>
-      <c r="C330" s="2" t="n">
+      <c r="C330" s="8" t="n">
         <v>54.21</v>
       </c>
       <c r="D330" t="n">
@@ -9801,7 +10406,7 @@
           <t>Philosophy</t>
         </is>
       </c>
-      <c r="C331" s="2" t="n">
+      <c r="C331" s="8" t="n">
         <v>20.02</v>
       </c>
       <c r="D331" t="n">
@@ -9829,7 +10434,7 @@
           <t>Philosophy</t>
         </is>
       </c>
-      <c r="C332" s="2" t="n">
+      <c r="C332" s="8" t="n">
         <v>15.94</v>
       </c>
       <c r="D332" t="n">
@@ -9857,7 +10462,7 @@
           <t>Philosophy</t>
         </is>
       </c>
-      <c r="C333" s="2" t="n">
+      <c r="C333" s="8" t="n">
         <v>58.11</v>
       </c>
       <c r="D333" t="n">
@@ -9885,7 +10490,7 @@
           <t>Philosophy</t>
         </is>
       </c>
-      <c r="C334" s="2" t="n">
+      <c r="C334" s="8" t="n">
         <v>36.34</v>
       </c>
       <c r="D334" t="n">
@@ -9913,7 +10518,7 @@
           <t>Philosophy</t>
         </is>
       </c>
-      <c r="C335" s="2" t="n">
+      <c r="C335" s="8" t="n">
         <v>17.44</v>
       </c>
       <c r="D335" t="n">
@@ -9941,7 +10546,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C336" s="2" t="n">
+      <c r="C336" s="8" t="n">
         <v>51.77</v>
       </c>
       <c r="D336" t="n">
@@ -9969,7 +10574,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C337" s="2" t="n">
+      <c r="C337" s="8" t="n">
         <v>17.49</v>
       </c>
       <c r="D337" t="n">
@@ -9997,7 +10602,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C338" s="2" t="n">
+      <c r="C338" s="8" t="n">
         <v>40.45</v>
       </c>
       <c r="D338" t="n">
@@ -10025,7 +10630,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C339" s="2" t="n">
+      <c r="C339" s="8" t="n">
         <v>51.17</v>
       </c>
       <c r="D339" t="n">
@@ -10053,7 +10658,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C340" s="2" t="n">
+      <c r="C340" s="8" t="n">
         <v>29.04</v>
       </c>
       <c r="D340" t="n">
@@ -10081,7 +10686,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C341" s="2" t="n">
+      <c r="C341" s="8" t="n">
         <v>41.05</v>
       </c>
       <c r="D341" t="n">
@@ -10109,7 +10714,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C342" s="2" t="n">
+      <c r="C342" s="8" t="n">
         <v>23.88</v>
       </c>
       <c r="D342" t="n">
@@ -10137,7 +10742,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C343" s="2" t="n">
+      <c r="C343" s="8" t="n">
         <v>53.64</v>
       </c>
       <c r="D343" t="n">
@@ -10165,7 +10770,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C344" s="2" t="n">
+      <c r="C344" s="8" t="n">
         <v>14.19</v>
       </c>
       <c r="D344" t="n">
@@ -10193,7 +10798,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C345" s="2" t="n">
+      <c r="C345" s="8" t="n">
         <v>50.89</v>
       </c>
       <c r="D345" t="n">
@@ -10221,7 +10826,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C346" s="2" t="n">
+      <c r="C346" s="8" t="n">
         <v>20.66</v>
       </c>
       <c r="D346" t="n">
@@ -10249,7 +10854,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C347" s="2" t="n">
+      <c r="C347" s="8" t="n">
         <v>57.31</v>
       </c>
       <c r="D347" t="n">
@@ -10277,7 +10882,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C348" s="2" t="n">
+      <c r="C348" s="8" t="n">
         <v>52.15</v>
       </c>
       <c r="D348" t="n">
@@ -10305,7 +10910,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C349" s="2" t="n">
+      <c r="C349" s="8" t="n">
         <v>15.42</v>
       </c>
       <c r="D349" t="n">
@@ -10333,7 +10938,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C350" s="2" t="n">
+      <c r="C350" s="8" t="n">
         <v>38.77</v>
       </c>
       <c r="D350" t="n">
@@ -10361,7 +10966,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C351" s="2" t="n">
+      <c r="C351" s="8" t="n">
         <v>30.95</v>
       </c>
       <c r="D351" t="n">
@@ -10389,7 +10994,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C352" s="2" t="n">
+      <c r="C352" s="8" t="n">
         <v>14.27</v>
       </c>
       <c r="D352" t="n">
@@ -10417,7 +11022,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C353" s="2" t="n">
+      <c r="C353" s="8" t="n">
         <v>33.63</v>
       </c>
       <c r="D353" t="n">
@@ -10445,7 +11050,7 @@
           <t>Poetry</t>
         </is>
       </c>
-      <c r="C354" s="2" t="n">
+      <c r="C354" s="8" t="n">
         <v>46.78</v>
       </c>
       <c r="D354" t="n">
@@ -10473,7 +11078,7 @@
           <t>Politics</t>
         </is>
       </c>
-      <c r="C355" s="2" t="n">
+      <c r="C355" s="8" t="n">
         <v>56.86</v>
       </c>
       <c r="D355" t="n">
@@ -10501,7 +11106,7 @@
           <t>Politics</t>
         </is>
       </c>
-      <c r="C356" s="2" t="n">
+      <c r="C356" s="8" t="n">
         <v>51.33</v>
       </c>
       <c r="D356" t="n">
@@ -10529,7 +11134,7 @@
           <t>Politics</t>
         </is>
       </c>
-      <c r="C357" s="2" t="n">
+      <c r="C357" s="8" t="n">
         <v>52.65</v>
       </c>
       <c r="D357" t="n">
@@ -10557,7 +11162,7 @@
           <t>Psychology</t>
         </is>
       </c>
-      <c r="C358" s="2" t="n">
+      <c r="C358" s="8" t="n">
         <v>31.04</v>
       </c>
       <c r="D358" t="n">
@@ -10585,7 +11190,7 @@
           <t>Psychology</t>
         </is>
       </c>
-      <c r="C359" s="2" t="n">
+      <c r="C359" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="D359" t="n">
@@ -10613,7 +11218,7 @@
           <t>Psychology</t>
         </is>
       </c>
-      <c r="C360" s="2" t="n">
+      <c r="C360" s="8" t="n">
         <v>59.95</v>
       </c>
       <c r="D360" t="n">
@@ -10641,7 +11246,7 @@
           <t>Psychology</t>
         </is>
       </c>
-      <c r="C361" s="2" t="n">
+      <c r="C361" s="8" t="n">
         <v>56.27</v>
       </c>
       <c r="D361" t="n">
@@ -10669,7 +11274,7 @@
           <t>Psychology</t>
         </is>
       </c>
-      <c r="C362" s="2" t="n">
+      <c r="C362" s="8" t="n">
         <v>39.43</v>
       </c>
       <c r="D362" t="n">
@@ -10697,7 +11302,7 @@
           <t>Psychology</t>
         </is>
       </c>
-      <c r="C363" s="2" t="n">
+      <c r="C363" s="8" t="n">
         <v>10.4</v>
       </c>
       <c r="D363" t="n">
@@ -10725,7 +11330,7 @@
           <t>Psychology</t>
         </is>
       </c>
-      <c r="C364" s="2" t="n">
+      <c r="C364" s="8" t="n">
         <v>21.14</v>
       </c>
       <c r="D364" t="n">
@@ -10753,7 +11358,7 @@
           <t>Religion</t>
         </is>
       </c>
-      <c r="C365" s="2" t="n">
+      <c r="C365" s="8" t="n">
         <v>27.62</v>
       </c>
       <c r="D365" t="n">
@@ -10781,7 +11386,7 @@
           <t>Religion</t>
         </is>
       </c>
-      <c r="C366" s="2" t="n">
+      <c r="C366" s="8" t="n">
         <v>28.42</v>
       </c>
       <c r="D366" t="n">
@@ -10809,7 +11414,7 @@
           <t>Religion</t>
         </is>
       </c>
-      <c r="C367" s="2" t="n">
+      <c r="C367" s="8" t="n">
         <v>37.97</v>
       </c>
       <c r="D367" t="n">
@@ -10837,7 +11442,7 @@
           <t>Religion</t>
         </is>
       </c>
-      <c r="C368" s="2" t="n">
+      <c r="C368" s="8" t="n">
         <v>30.03</v>
       </c>
       <c r="D368" t="n">
@@ -10865,7 +11470,7 @@
           <t>Religion</t>
         </is>
       </c>
-      <c r="C369" s="2" t="n">
+      <c r="C369" s="8" t="n">
         <v>57.49</v>
       </c>
       <c r="D369" t="n">
@@ -10893,7 +11498,7 @@
           <t>Religion</t>
         </is>
       </c>
-      <c r="C370" s="2" t="n">
+      <c r="C370" s="8" t="n">
         <v>24.57</v>
       </c>
       <c r="D370" t="n">
@@ -10921,7 +11526,7 @@
           <t>Religion</t>
         </is>
       </c>
-      <c r="C371" s="2" t="n">
+      <c r="C371" s="8" t="n">
         <v>21.87</v>
       </c>
       <c r="D371" t="n">
@@ -10949,7 +11554,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C372" s="2" t="n">
+      <c r="C372" s="8" t="n">
         <v>14.75</v>
       </c>
       <c r="D372" t="n">
@@ -10977,7 +11582,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C373" s="2" t="n">
+      <c r="C373" s="8" t="n">
         <v>31.3</v>
       </c>
       <c r="D373" t="n">
@@ -11005,7 +11610,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C374" s="2" t="n">
+      <c r="C374" s="8" t="n">
         <v>34.53</v>
       </c>
       <c r="D374" t="n">
@@ -11033,7 +11638,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C375" s="2" t="n">
+      <c r="C375" s="8" t="n">
         <v>13.38</v>
       </c>
       <c r="D375" t="n">
@@ -11061,7 +11666,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C376" s="2" t="n">
+      <c r="C376" s="8" t="n">
         <v>25.27</v>
       </c>
       <c r="D376" t="n">
@@ -11089,7 +11694,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C377" s="2" t="n">
+      <c r="C377" s="8" t="n">
         <v>12.87</v>
       </c>
       <c r="D377" t="n">
@@ -11117,7 +11722,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C378" s="2" t="n">
+      <c r="C378" s="8" t="n">
         <v>40.83</v>
       </c>
       <c r="D378" t="n">
@@ -11145,7 +11750,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C379" s="2" t="n">
+      <c r="C379" s="8" t="n">
         <v>35.61</v>
       </c>
       <c r="D379" t="n">
@@ -11173,7 +11778,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C380" s="2" t="n">
+      <c r="C380" s="8" t="n">
         <v>21.96</v>
       </c>
       <c r="D380" t="n">
@@ -11201,7 +11806,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C381" s="2" t="n">
+      <c r="C381" s="8" t="n">
         <v>15.97</v>
       </c>
       <c r="D381" t="n">
@@ -11229,7 +11834,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C382" s="2" t="n">
+      <c r="C382" s="8" t="n">
         <v>33.97</v>
       </c>
       <c r="D382" t="n">
@@ -11257,7 +11862,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C383" s="2" t="n">
+      <c r="C383" s="8" t="n">
         <v>28.82</v>
       </c>
       <c r="D383" t="n">
@@ -11285,7 +11890,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C384" s="2" t="n">
+      <c r="C384" s="8" t="n">
         <v>47.67</v>
       </c>
       <c r="D384" t="n">
@@ -11313,7 +11918,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C385" s="2" t="n">
+      <c r="C385" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="D385" t="n">
@@ -11341,7 +11946,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C386" s="2" t="n">
+      <c r="C386" s="8" t="n">
         <v>16.24</v>
       </c>
       <c r="D386" t="n">
@@ -11369,7 +11974,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C387" s="2" t="n">
+      <c r="C387" s="8" t="n">
         <v>55.99</v>
       </c>
       <c r="D387" t="n">
@@ -11397,7 +12002,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C388" s="2" t="n">
+      <c r="C388" s="8" t="n">
         <v>53.98</v>
       </c>
       <c r="D388" t="n">
@@ -11425,7 +12030,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C389" s="2" t="n">
+      <c r="C389" s="8" t="n">
         <v>59.99</v>
       </c>
       <c r="D389" t="n">
@@ -11453,7 +12058,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C390" s="2" t="n">
+      <c r="C390" s="8" t="n">
         <v>24.12</v>
       </c>
       <c r="D390" t="n">
@@ -11481,7 +12086,7 @@
           <t>Romance</t>
         </is>
       </c>
-      <c r="C391" s="2" t="n">
+      <c r="C391" s="8" t="n">
         <v>32.61</v>
       </c>
       <c r="D391" t="n">
@@ -11509,7 +12114,7 @@
           <t>Science</t>
         </is>
       </c>
-      <c r="C392" s="2" t="n">
+      <c r="C392" s="8" t="n">
         <v>28.41</v>
       </c>
       <c r="D392" t="n">
@@ -11537,7 +12142,7 @@
           <t>Science</t>
         </is>
       </c>
-      <c r="C393" s="2" t="n">
+      <c r="C393" s="8" t="n">
         <v>57.36</v>
       </c>
       <c r="D393" t="n">
@@ -11565,7 +12170,7 @@
           <t>Science</t>
         </is>
       </c>
-      <c r="C394" s="2" t="n">
+      <c r="C394" s="8" t="n">
         <v>16.28</v>
       </c>
       <c r="D394" t="n">
@@ -11593,7 +12198,7 @@
           <t>Science</t>
         </is>
       </c>
-      <c r="C395" s="2" t="n">
+      <c r="C395" s="8" t="n">
         <v>30.6</v>
       </c>
       <c r="D395" t="n">
@@ -11621,7 +12226,7 @@
           <t>Science</t>
         </is>
       </c>
-      <c r="C396" s="2" t="n">
+      <c r="C396" s="8" t="n">
         <v>44.74</v>
       </c>
       <c r="D396" t="n">
@@ -11649,7 +12254,7 @@
           <t>Science</t>
         </is>
       </c>
-      <c r="C397" s="2" t="n">
+      <c r="C397" s="8" t="n">
         <v>25.83</v>
       </c>
       <c r="D397" t="n">
@@ -11677,7 +12282,7 @@
           <t>Science</t>
         </is>
       </c>
-      <c r="C398" s="2" t="n">
+      <c r="C398" s="8" t="n">
         <v>57.35</v>
       </c>
       <c r="D398" t="n">
@@ -11705,7 +12310,7 @@
           <t>Science</t>
         </is>
       </c>
-      <c r="C399" s="2" t="n">
+      <c r="C399" s="8" t="n">
         <v>13.03</v>
       </c>
       <c r="D399" t="n">
@@ -11733,7 +12338,7 @@
           <t>Science</t>
         </is>
       </c>
-      <c r="C400" s="2" t="n">
+      <c r="C400" s="8" t="n">
         <v>55.91</v>
       </c>
       <c r="D400" t="n">
@@ -11761,7 +12366,7 @@
           <t>Science</t>
         </is>
       </c>
-      <c r="C401" s="2" t="n">
+      <c r="C401" s="8" t="n">
         <v>13.76</v>
       </c>
       <c r="D401" t="n">
@@ -11789,7 +12394,7 @@
           <t>Science</t>
         </is>
       </c>
-      <c r="C402" s="2" t="n">
+      <c r="C402" s="8" t="n">
         <v>42.96</v>
       </c>
       <c r="D402" t="n">
@@ -11817,7 +12422,7 @@
           <t>Science</t>
         </is>
       </c>
-      <c r="C403" s="2" t="n">
+      <c r="C403" s="8" t="n">
         <v>10.01</v>
       </c>
       <c r="D403" t="n">
@@ -11845,7 +12450,7 @@
           <t>Science</t>
         </is>
       </c>
-      <c r="C404" s="2" t="n">
+      <c r="C404" s="8" t="n">
         <v>29.45</v>
       </c>
       <c r="D404" t="n">
@@ -11873,7 +12478,7 @@
           <t>Science</t>
         </is>
       </c>
-      <c r="C405" s="2" t="n">
+      <c r="C405" s="8" t="n">
         <v>37.55</v>
       </c>
       <c r="D405" t="n">
@@ -11901,7 +12506,7 @@
           <t>Science Fiction</t>
         </is>
       </c>
-      <c r="C406" s="2" t="n">
+      <c r="C406" s="8" t="n">
         <v>21.36</v>
       </c>
       <c r="D406" t="n">
@@ -11929,7 +12534,7 @@
           <t>Science Fiction</t>
         </is>
       </c>
-      <c r="C407" s="2" t="n">
+      <c r="C407" s="8" t="n">
         <v>51.48</v>
       </c>
       <c r="D407" t="n">
@@ -11957,7 +12562,7 @@
           <t>Science Fiction</t>
         </is>
       </c>
-      <c r="C408" s="2" t="n">
+      <c r="C408" s="8" t="n">
         <v>54.86</v>
       </c>
       <c r="D408" t="n">
@@ -11985,7 +12590,7 @@
           <t>Science Fiction</t>
         </is>
       </c>
-      <c r="C409" s="2" t="n">
+      <c r="C409" s="8" t="n">
         <v>32.42</v>
       </c>
       <c r="D409" t="n">
@@ -12013,7 +12618,7 @@
           <t>Science Fiction</t>
         </is>
       </c>
-      <c r="C410" s="2" t="n">
+      <c r="C410" s="8" t="n">
         <v>34.96</v>
       </c>
       <c r="D410" t="n">
@@ -12041,7 +12646,7 @@
           <t>Science Fiction</t>
         </is>
       </c>
-      <c r="C411" s="2" t="n">
+      <c r="C411" s="8" t="n">
         <v>35.67</v>
       </c>
       <c r="D411" t="n">
@@ -12069,7 +12674,7 @@
           <t>Science Fiction</t>
         </is>
       </c>
-      <c r="C412" s="2" t="n">
+      <c r="C412" s="8" t="n">
         <v>33.26</v>
       </c>
       <c r="D412" t="n">
@@ -12097,7 +12702,7 @@
           <t>Science Fiction</t>
         </is>
       </c>
-      <c r="C413" s="2" t="n">
+      <c r="C413" s="8" t="n">
         <v>37.59</v>
       </c>
       <c r="D413" t="n">
@@ -12125,7 +12730,7 @@
           <t>Science Fiction</t>
         </is>
       </c>
-      <c r="C414" s="2" t="n">
+      <c r="C414" s="8" t="n">
         <v>19.07</v>
       </c>
       <c r="D414" t="n">
@@ -12153,7 +12758,7 @@
           <t>Science Fiction</t>
         </is>
       </c>
-      <c r="C415" s="2" t="n">
+      <c r="C415" s="8" t="n">
         <v>48.74</v>
       </c>
       <c r="D415" t="n">
@@ -12181,7 +12786,7 @@
           <t>Science Fiction</t>
         </is>
       </c>
-      <c r="C416" s="2" t="n">
+      <c r="C416" s="8" t="n">
         <v>26.12</v>
       </c>
       <c r="D416" t="n">
@@ -12209,7 +12814,7 @@
           <t>Science Fiction</t>
         </is>
       </c>
-      <c r="C417" s="2" t="n">
+      <c r="C417" s="8" t="n">
         <v>36.26</v>
       </c>
       <c r="D417" t="n">
@@ -12237,7 +12842,7 @@
           <t>Science Fiction</t>
         </is>
       </c>
-      <c r="C418" s="2" t="n">
+      <c r="C418" s="8" t="n">
         <v>10.65</v>
       </c>
       <c r="D418" t="n">
@@ -12265,7 +12870,7 @@
           <t>Science Fiction</t>
         </is>
       </c>
-      <c r="C419" s="2" t="n">
+      <c r="C419" s="8" t="n">
         <v>10.92</v>
       </c>
       <c r="D419" t="n">
@@ -12293,7 +12898,7 @@
           <t>Science Fiction</t>
         </is>
       </c>
-      <c r="C420" s="2" t="n">
+      <c r="C420" s="8" t="n">
         <v>44.18</v>
       </c>
       <c r="D420" t="n">
@@ -12321,7 +12926,7 @@
           <t>Science Fiction</t>
         </is>
       </c>
-      <c r="C421" s="2" t="n">
+      <c r="C421" s="8" t="n">
         <v>43.3</v>
       </c>
       <c r="D421" t="n">
@@ -12349,7 +12954,7 @@
           <t>Self Help</t>
         </is>
       </c>
-      <c r="C422" s="2" t="n">
+      <c r="C422" s="8" t="n">
         <v>46.03</v>
       </c>
       <c r="D422" t="n">
@@ -12377,7 +12982,7 @@
           <t>Self Help</t>
         </is>
       </c>
-      <c r="C423" s="2" t="n">
+      <c r="C423" s="8" t="n">
         <v>46.49</v>
       </c>
       <c r="D423" t="n">
@@ -12405,7 +13010,7 @@
           <t>Self Help</t>
         </is>
       </c>
-      <c r="C424" s="2" t="n">
+      <c r="C424" s="8" t="n">
         <v>46.35</v>
       </c>
       <c r="D424" t="n">
@@ -12433,7 +13038,7 @@
           <t>Self Help</t>
         </is>
       </c>
-      <c r="C425" s="2" t="n">
+      <c r="C425" s="8" t="n">
         <v>52.15</v>
       </c>
       <c r="D425" t="n">
@@ -12461,7 +13066,7 @@
           <t>Self Help</t>
         </is>
       </c>
-      <c r="C426" s="2" t="n">
+      <c r="C426" s="8" t="n">
         <v>12.08</v>
       </c>
       <c r="D426" t="n">
@@ -12489,7 +13094,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C427" s="2" t="n">
+      <c r="C427" s="8" t="n">
         <v>17.08</v>
       </c>
       <c r="D427" t="n">
@@ -12517,7 +13122,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C428" s="2" t="n">
+      <c r="C428" s="8" t="n">
         <v>36.72</v>
       </c>
       <c r="D428" t="n">
@@ -12545,7 +13150,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C429" s="2" t="n">
+      <c r="C429" s="8" t="n">
         <v>51.99</v>
       </c>
       <c r="D429" t="n">
@@ -12573,7 +13178,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C430" s="2" t="n">
+      <c r="C430" s="8" t="n">
         <v>22.11</v>
       </c>
       <c r="D430" t="n">
@@ -12601,7 +13206,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C431" s="2" t="n">
+      <c r="C431" s="8" t="n">
         <v>29.17</v>
       </c>
       <c r="D431" t="n">
@@ -12629,7 +13234,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C432" s="2" t="n">
+      <c r="C432" s="8" t="n">
         <v>54.63</v>
       </c>
       <c r="D432" t="n">
@@ -12657,7 +13262,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C433" s="2" t="n">
+      <c r="C433" s="8" t="n">
         <v>19.92</v>
       </c>
       <c r="D433" t="n">
@@ -12685,7 +13290,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C434" s="2" t="n">
+      <c r="C434" s="8" t="n">
         <v>45.61</v>
       </c>
       <c r="D434" t="n">
@@ -12713,7 +13318,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C435" s="2" t="n">
+      <c r="C435" s="8" t="n">
         <v>46.91</v>
       </c>
       <c r="D435" t="n">
@@ -12741,7 +13346,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C436" s="2" t="n">
+      <c r="C436" s="8" t="n">
         <v>15.44</v>
       </c>
       <c r="D436" t="n">
@@ -12769,7 +13374,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C437" s="2" t="n">
+      <c r="C437" s="8" t="n">
         <v>10.16</v>
       </c>
       <c r="D437" t="n">
@@ -12797,7 +13402,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C438" s="2" t="n">
+      <c r="C438" s="8" t="n">
         <v>18.97</v>
       </c>
       <c r="D438" t="n">
@@ -12825,7 +13430,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C439" s="2" t="n">
+      <c r="C439" s="8" t="n">
         <v>13.61</v>
       </c>
       <c r="D439" t="n">
@@ -12853,7 +13458,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C440" s="2" t="n">
+      <c r="C440" s="8" t="n">
         <v>50.4</v>
       </c>
       <c r="D440" t="n">
@@ -12881,7 +13486,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C441" s="2" t="n">
+      <c r="C441" s="8" t="n">
         <v>51.04</v>
       </c>
       <c r="D441" t="n">
@@ -12909,7 +13514,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C442" s="2" t="n">
+      <c r="C442" s="8" t="n">
         <v>52.29</v>
       </c>
       <c r="D442" t="n">
@@ -12937,7 +13542,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C443" s="2" t="n">
+      <c r="C443" s="8" t="n">
         <v>38.16</v>
       </c>
       <c r="D443" t="n">
@@ -12965,7 +13570,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C444" s="2" t="n">
+      <c r="C444" s="8" t="n">
         <v>19.49</v>
       </c>
       <c r="D444" t="n">
@@ -12993,7 +13598,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C445" s="2" t="n">
+      <c r="C445" s="8" t="n">
         <v>16.28</v>
       </c>
       <c r="D445" t="n">
@@ -13021,7 +13626,7 @@
           <t>Sequential Art</t>
         </is>
       </c>
-      <c r="C446" s="2" t="n">
+      <c r="C446" s="8" t="n">
         <v>48.41</v>
       </c>
       <c r="D446" t="n">
@@ -13049,7 +13654,7 @@
           <t>Short Stories</t>
         </is>
       </c>
-      <c r="C447" s="2" t="n">
+      <c r="C447" s="8" t="n">
         <v>35.88</v>
       </c>
       <c r="D447" t="n">
@@ -13077,7 +13682,7 @@
           <t>Spirituality</t>
         </is>
       </c>
-      <c r="C448" s="2" t="n">
+      <c r="C448" s="8" t="n">
         <v>55.65</v>
       </c>
       <c r="D448" t="n">
@@ -13105,7 +13710,7 @@
           <t>Spirituality</t>
         </is>
       </c>
-      <c r="C449" s="2" t="n">
+      <c r="C449" s="8" t="n">
         <v>37.8</v>
       </c>
       <c r="D449" t="n">
@@ -13133,7 +13738,7 @@
           <t>Spirituality</t>
         </is>
       </c>
-      <c r="C450" s="2" t="n">
+      <c r="C450" s="8" t="n">
         <v>20.91</v>
       </c>
       <c r="D450" t="n">
@@ -13161,7 +13766,7 @@
           <t>Spirituality</t>
         </is>
       </c>
-      <c r="C451" s="2" t="n">
+      <c r="C451" s="8" t="n">
         <v>32.24</v>
       </c>
       <c r="D451" t="n">
@@ -13189,7 +13794,7 @@
           <t>Spirituality</t>
         </is>
       </c>
-      <c r="C452" s="2" t="n">
+      <c r="C452" s="8" t="n">
         <v>17.66</v>
       </c>
       <c r="D452" t="n">
@@ -13217,7 +13822,7 @@
           <t>Spirituality</t>
         </is>
       </c>
-      <c r="C453" s="2" t="n">
+      <c r="C453" s="8" t="n">
         <v>46.33</v>
       </c>
       <c r="D453" t="n">
@@ -13245,7 +13850,7 @@
           <t>Sports and Games</t>
         </is>
       </c>
-      <c r="C454" s="2" t="n">
+      <c r="C454" s="8" t="n">
         <v>51.22</v>
       </c>
       <c r="D454" t="n">
@@ -13273,7 +13878,7 @@
           <t>Sports and Games</t>
         </is>
       </c>
-      <c r="C455" s="2" t="n">
+      <c r="C455" s="8" t="n">
         <v>40.44</v>
       </c>
       <c r="D455" t="n">
@@ -13301,7 +13906,7 @@
           <t>Sports and Games</t>
         </is>
       </c>
-      <c r="C456" s="2" t="n">
+      <c r="C456" s="8" t="n">
         <v>44.91</v>
       </c>
       <c r="D456" t="n">
@@ -13329,7 +13934,7 @@
           <t>Sports and Games</t>
         </is>
       </c>
-      <c r="C457" s="2" t="n">
+      <c r="C457" s="8" t="n">
         <v>24.42</v>
       </c>
       <c r="D457" t="n">
@@ -13357,7 +13962,7 @@
           <t>Sports and Games</t>
         </is>
       </c>
-      <c r="C458" s="2" t="n">
+      <c r="C458" s="8" t="n">
         <v>44.84</v>
       </c>
       <c r="D458" t="n">
@@ -13385,7 +13990,7 @@
           <t>Suspense</t>
         </is>
       </c>
-      <c r="C459" s="2" t="n">
+      <c r="C459" s="8" t="n">
         <v>58.33</v>
       </c>
       <c r="D459" t="n">
@@ -13413,7 +14018,7 @@
           <t>Thriller</t>
         </is>
       </c>
-      <c r="C460" s="2" t="n">
+      <c r="C460" s="8" t="n">
         <v>52.22</v>
       </c>
       <c r="D460" t="n">
@@ -13441,7 +14046,7 @@
           <t>Thriller</t>
         </is>
       </c>
-      <c r="C461" s="2" t="n">
+      <c r="C461" s="8" t="n">
         <v>34.93</v>
       </c>
       <c r="D461" t="n">
@@ -13469,7 +14074,7 @@
           <t>Thriller</t>
         </is>
       </c>
-      <c r="C462" s="2" t="n">
+      <c r="C462" s="8" t="n">
         <v>18.32</v>
       </c>
       <c r="D462" t="n">
@@ -13497,7 +14102,7 @@
           <t>Thriller</t>
         </is>
       </c>
-      <c r="C463" s="2" t="n">
+      <c r="C463" s="8" t="n">
         <v>12.84</v>
       </c>
       <c r="D463" t="n">
@@ -13525,7 +14130,7 @@
           <t>Thriller</t>
         </is>
       </c>
-      <c r="C464" s="2" t="n">
+      <c r="C464" s="8" t="n">
         <v>31.49</v>
       </c>
       <c r="D464" t="n">
@@ -13553,7 +14158,7 @@
           <t>Thriller</t>
         </is>
       </c>
-      <c r="C465" s="2" t="n">
+      <c r="C465" s="8" t="n">
         <v>39.24</v>
       </c>
       <c r="D465" t="n">
@@ -13581,7 +14186,7 @@
           <t>Thriller</t>
         </is>
       </c>
-      <c r="C466" s="2" t="n">
+      <c r="C466" s="8" t="n">
         <v>59.71</v>
       </c>
       <c r="D466" t="n">
@@ -13609,7 +14214,7 @@
           <t>Thriller</t>
         </is>
       </c>
-      <c r="C467" s="2" t="n">
+      <c r="C467" s="8" t="n">
         <v>23.82</v>
       </c>
       <c r="D467" t="n">
@@ -13637,7 +14242,7 @@
           <t>Thriller</t>
         </is>
       </c>
-      <c r="C468" s="2" t="n">
+      <c r="C468" s="8" t="n">
         <v>13.82</v>
       </c>
       <c r="D468" t="n">
@@ -13665,7 +14270,7 @@
           <t>Thriller</t>
         </is>
       </c>
-      <c r="C469" s="2" t="n">
+      <c r="C469" s="8" t="n">
         <v>15.77</v>
       </c>
       <c r="D469" t="n">
@@ -13693,7 +14298,7 @@
           <t>Thriller</t>
         </is>
       </c>
-      <c r="C470" s="2" t="n">
+      <c r="C470" s="8" t="n">
         <v>43.61</v>
       </c>
       <c r="D470" t="n">
@@ -13721,7 +14326,7 @@
           <t>Travel</t>
         </is>
       </c>
-      <c r="C471" s="2" t="n">
+      <c r="C471" s="8" t="n">
         <v>26.08</v>
       </c>
       <c r="D471" t="n">
@@ -13749,7 +14354,7 @@
           <t>Travel</t>
         </is>
       </c>
-      <c r="C472" s="2" t="n">
+      <c r="C472" s="8" t="n">
         <v>44.34</v>
       </c>
       <c r="D472" t="n">
@@ -13777,7 +14382,7 @@
           <t>Travel</t>
         </is>
       </c>
-      <c r="C473" s="2" t="n">
+      <c r="C473" s="8" t="n">
         <v>56.88</v>
       </c>
       <c r="D473" t="n">
@@ -13805,7 +14410,7 @@
           <t>Travel</t>
         </is>
       </c>
-      <c r="C474" s="2" t="n">
+      <c r="C474" s="8" t="n">
         <v>49.43</v>
       </c>
       <c r="D474" t="n">
@@ -13833,7 +14438,7 @@
           <t>Travel</t>
         </is>
       </c>
-      <c r="C475" s="2" t="n">
+      <c r="C475" s="8" t="n">
         <v>45.17</v>
       </c>
       <c r="D475" t="n">
@@ -13861,7 +14466,7 @@
           <t>Travel</t>
         </is>
       </c>
-      <c r="C476" s="2" t="n">
+      <c r="C476" s="8" t="n">
         <v>38.95</v>
       </c>
       <c r="D476" t="n">
@@ -13889,7 +14494,7 @@
           <t>Travel</t>
         </is>
       </c>
-      <c r="C477" s="2" t="n">
+      <c r="C477" s="8" t="n">
         <v>48.87</v>
       </c>
       <c r="D477" t="n">
@@ -13917,7 +14522,7 @@
           <t>Travel</t>
         </is>
       </c>
-      <c r="C478" s="2" t="n">
+      <c r="C478" s="8" t="n">
         <v>30.54</v>
       </c>
       <c r="D478" t="n">
@@ -13945,7 +14550,7 @@
           <t>Travel</t>
         </is>
       </c>
-      <c r="C479" s="2" t="n">
+      <c r="C479" s="8" t="n">
         <v>23.21</v>
       </c>
       <c r="D479" t="n">
@@ -13973,7 +14578,7 @@
           <t>Travel</t>
         </is>
       </c>
-      <c r="C480" s="2" t="n">
+      <c r="C480" s="8" t="n">
         <v>37.33</v>
       </c>
       <c r="D480" t="n">
@@ -14001,7 +14606,7 @@
           <t>Travel</t>
         </is>
       </c>
-      <c r="C481" s="2" t="n">
+      <c r="C481" s="8" t="n">
         <v>36.94</v>
       </c>
       <c r="D481" t="n">
@@ -14029,7 +14634,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C482" s="2" t="n">
+      <c r="C482" s="8" t="n">
         <v>29.82</v>
       </c>
       <c r="D482" t="n">
@@ -14057,7 +14662,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C483" s="2" t="n">
+      <c r="C483" s="8" t="n">
         <v>21.94</v>
       </c>
       <c r="D483" t="n">
@@ -14085,7 +14690,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C484" s="2" t="n">
+      <c r="C484" s="8" t="n">
         <v>48.49</v>
       </c>
       <c r="D484" t="n">
@@ -14113,7 +14718,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C485" s="2" t="n">
+      <c r="C485" s="8" t="n">
         <v>57.36</v>
       </c>
       <c r="D485" t="n">
@@ -14141,7 +14746,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C486" s="2" t="n">
+      <c r="C486" s="8" t="n">
         <v>19.69</v>
       </c>
       <c r="D486" t="n">
@@ -14169,7 +14774,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C487" s="2" t="n">
+      <c r="C487" s="8" t="n">
         <v>20.46</v>
       </c>
       <c r="D487" t="n">
@@ -14197,7 +14802,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C488" s="2" t="n">
+      <c r="C488" s="8" t="n">
         <v>43.58</v>
       </c>
       <c r="D488" t="n">
@@ -14225,7 +14830,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C489" s="2" t="n">
+      <c r="C489" s="8" t="n">
         <v>48.39</v>
       </c>
       <c r="D489" t="n">
@@ -14253,7 +14858,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C490" s="2" t="n">
+      <c r="C490" s="8" t="n">
         <v>13.73</v>
       </c>
       <c r="D490" t="n">
@@ -14281,7 +14886,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C491" s="2" t="n">
+      <c r="C491" s="8" t="n">
         <v>54.62</v>
       </c>
       <c r="D491" t="n">
@@ -14309,7 +14914,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C492" s="2" t="n">
+      <c r="C492" s="8" t="n">
         <v>48.96</v>
       </c>
       <c r="D492" t="n">
@@ -14337,7 +14942,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C493" s="2" t="n">
+      <c r="C493" s="8" t="n">
         <v>44.29</v>
       </c>
       <c r="D493" t="n">
@@ -14365,7 +14970,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C494" s="2" t="n">
+      <c r="C494" s="8" t="n">
         <v>19.18</v>
       </c>
       <c r="D494" t="n">
@@ -14393,7 +14998,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C495" s="2" t="n">
+      <c r="C495" s="8" t="n">
         <v>52.53</v>
       </c>
       <c r="D495" t="n">
@@ -14421,7 +15026,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C496" s="2" t="n">
+      <c r="C496" s="8" t="n">
         <v>45.75</v>
       </c>
       <c r="D496" t="n">
@@ -14449,7 +15054,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C497" s="2" t="n">
+      <c r="C497" s="8" t="n">
         <v>42.8</v>
       </c>
       <c r="D497" t="n">
@@ -14477,7 +15082,7 @@
           <t>Womens Fiction</t>
         </is>
       </c>
-      <c r="C498" s="2" t="n">
+      <c r="C498" s="8" t="n">
         <v>13.86</v>
       </c>
       <c r="D498" t="n">
@@ -14505,7 +15110,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C499" s="2" t="n">
+      <c r="C499" s="8" t="n">
         <v>28.13</v>
       </c>
       <c r="D499" t="n">
@@ -14533,7 +15138,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C500" s="2" t="n">
+      <c r="C500" s="8" t="n">
         <v>58.14</v>
       </c>
       <c r="D500" t="n">
@@ -14561,7 +15166,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C501" s="2" t="n">
+      <c r="C501" s="8" t="n">
         <v>28.81</v>
       </c>
       <c r="D501" t="n">
@@ -14589,7 +15194,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C502" s="2" t="n">
+      <c r="C502" s="8" t="n">
         <v>50.83</v>
       </c>
       <c r="D502" t="n">
@@ -14617,7 +15222,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C503" s="2" t="n">
+      <c r="C503" s="8" t="n">
         <v>55.35</v>
       </c>
       <c r="D503" t="n">
@@ -14645,7 +15250,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C504" s="2" t="n">
+      <c r="C504" s="8" t="n">
         <v>29.99</v>
       </c>
       <c r="D504" t="n">
@@ -14673,7 +15278,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C505" s="2" t="n">
+      <c r="C505" s="8" t="n">
         <v>48.56</v>
       </c>
       <c r="D505" t="n">
@@ -14701,7 +15306,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C506" s="2" t="n">
+      <c r="C506" s="8" t="n">
         <v>40.36</v>
       </c>
       <c r="D506" t="n">
@@ -14729,7 +15334,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C507" s="2" t="n">
+      <c r="C507" s="8" t="n">
         <v>38.28</v>
       </c>
       <c r="D507" t="n">
@@ -14757,7 +15362,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C508" s="2" t="n">
+      <c r="C508" s="8" t="n">
         <v>14.86</v>
       </c>
       <c r="D508" t="n">
@@ -14785,7 +15390,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C509" s="2" t="n">
+      <c r="C509" s="8" t="n">
         <v>43.55</v>
       </c>
       <c r="D509" t="n">
@@ -14813,7 +15418,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C510" s="2" t="n">
+      <c r="C510" s="8" t="n">
         <v>17.46</v>
       </c>
       <c r="D510" t="n">
@@ -14841,7 +15446,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C511" s="2" t="n">
+      <c r="C511" s="8" t="n">
         <v>48.05</v>
       </c>
       <c r="D511" t="n">
@@ -14869,7 +15474,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C512" s="2" t="n">
+      <c r="C512" s="8" t="n">
         <v>35.35</v>
       </c>
       <c r="D512" t="n">
@@ -14897,7 +15502,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C513" s="2" t="n">
+      <c r="C513" s="8" t="n">
         <v>14.44</v>
       </c>
       <c r="D513" t="n">
@@ -14925,7 +15530,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C514" s="2" t="n">
+      <c r="C514" s="8" t="n">
         <v>45.22</v>
       </c>
       <c r="D514" t="n">
@@ -14953,7 +15558,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C515" s="2" t="n">
+      <c r="C515" s="8" t="n">
         <v>22.65</v>
       </c>
       <c r="D515" t="n">
@@ -14981,7 +15586,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C516" s="2" t="n">
+      <c r="C516" s="8" t="n">
         <v>27.12</v>
       </c>
       <c r="D516" t="n">
@@ -15009,7 +15614,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C517" s="2" t="n">
+      <c r="C517" s="8" t="n">
         <v>46.31</v>
       </c>
       <c r="D517" t="n">
@@ -15037,7 +15642,7 @@
           <t>Young Adult</t>
         </is>
       </c>
-      <c r="C518" s="2" t="n">
+      <c r="C518" s="8" t="n">
         <v>14.36</v>
       </c>
       <c r="D518" t="n">
@@ -15055,11 +15660,21 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C2:C518">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00C6E0B4"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15077,32 +15692,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Books</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Avg price</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Min price</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Max price</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>4-5 star share</t>
         </is>
@@ -15117,16 +15732,16 @@
       <c r="B2" t="n">
         <v>20</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="8" t="n">
         <v>32.794</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="8" t="n">
         <v>10.69</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="8" t="n">
         <v>59.48</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -15139,16 +15754,16 @@
       <c r="B3" t="n">
         <v>20</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="8" t="n">
         <v>35.379</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="8" t="n">
         <v>16.62</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="8" t="n">
         <v>55.55</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -15161,16 +15776,16 @@
       <c r="B4" t="n">
         <v>20</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="8" t="n">
         <v>32.91950000000001</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="8" t="n">
         <v>10.16</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="8" t="n">
         <v>54.63</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -15183,16 +15798,16 @@
       <c r="B5" t="n">
         <v>20</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="8" t="n">
         <v>31.038</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="8" t="n">
         <v>12.87</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="8" t="n">
         <v>59.99</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="9" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -15205,16 +15820,16 @@
       <c r="B6" t="n">
         <v>20</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="8" t="n">
         <v>37.69650000000001</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="8" t="n">
         <v>55.84</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="9" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -15227,16 +15842,16 @@
       <c r="B7" t="n">
         <v>20</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="8" t="n">
         <v>36.4025</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="8" t="n">
         <v>12.96</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="8" t="n">
         <v>58.08</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="9" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -15249,16 +15864,16 @@
       <c r="B8" t="n">
         <v>20</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="8" t="n">
         <v>32.69</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="8" t="n">
         <v>12.23</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="8" t="n">
         <v>56.06</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="9" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -15271,16 +15886,16 @@
       <c r="B9" t="n">
         <v>20</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="8" t="n">
         <v>35.024</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="8" t="n">
         <v>13.99</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="8" t="n">
         <v>56.76</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="9" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -15293,16 +15908,16 @@
       <c r="B10" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="8" t="n">
         <v>34.643</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="8" t="n">
         <v>14.07</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="8" t="n">
         <v>56.48</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="9" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -15315,16 +15930,16 @@
       <c r="B11" t="n">
         <v>20</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="8" t="n">
         <v>39.654</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="8" t="n">
         <v>13.34</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="8" t="n">
         <v>56.63</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="9" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -15337,16 +15952,16 @@
       <c r="B12" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="8" t="n">
         <v>35.39100000000001</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="8" t="n">
         <v>14.36</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="8" t="n">
         <v>58.14</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -15359,16 +15974,16 @@
       <c r="B13" t="n">
         <v>20</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="8" t="n">
         <v>31.399</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="8" t="n">
         <v>11.38</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="8" t="n">
         <v>56.41</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="9" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -15381,16 +15996,16 @@
       <c r="B14" t="n">
         <v>19</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="8" t="n">
         <v>36.54526315789474</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="8" t="n">
         <v>14.82</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="8" t="n">
         <v>58.63</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="9" t="n">
         <v>0.2105263157894737</v>
       </c>
     </row>
@@ -15403,16 +16018,16 @@
       <c r="B15" t="n">
         <v>19</v>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="8" t="n">
         <v>35.97421052631579</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="8" t="n">
         <v>14.19</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="8" t="n">
         <v>57.31</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="9" t="n">
         <v>0.631578947368421</v>
       </c>
     </row>
@@ -15425,16 +16040,16 @@
       <c r="B16" t="n">
         <v>18</v>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" s="8" t="n">
         <v>37.29499999999999</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="8" t="n">
         <v>11.45</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="8" t="n">
         <v>59.64</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="9" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -15447,16 +16062,16 @@
       <c r="B17" t="n">
         <v>17</v>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" s="8" t="n">
         <v>36.79117647058824</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="8" t="n">
         <v>13.73</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="8" t="n">
         <v>57.36</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="9" t="n">
         <v>0.5294117647058824</v>
       </c>
     </row>
@@ -15469,16 +16084,16 @@
       <c r="B18" t="n">
         <v>17</v>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="8" t="n">
         <v>35.94941176470588</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="8" t="n">
         <v>10.56</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="8" t="n">
         <v>57.86</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="9" t="n">
         <v>0.2941176470588235</v>
       </c>
     </row>
@@ -15491,16 +16106,16 @@
       <c r="B19" t="n">
         <v>16</v>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C19" s="8" t="n">
         <v>33.8025</v>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="8" t="n">
         <v>10.65</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="8" t="n">
         <v>54.86</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="9" t="n">
         <v>0.3125</v>
       </c>
     </row>
@@ -15513,16 +16128,16 @@
       <c r="B20" t="n">
         <v>14</v>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C20" s="8" t="n">
         <v>33.08857142857143</v>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="8" t="n">
         <v>10.01</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="8" t="n">
         <v>57.36</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="9" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -15535,16 +16150,16 @@
       <c r="B21" t="n">
         <v>13</v>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C21" s="8" t="n">
         <v>35.63692307692308</v>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="8" t="n">
         <v>12.36</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="8" t="n">
         <v>57.25</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="9" t="n">
         <v>0.3846153846153846</v>
       </c>
     </row>
@@ -15557,16 +16172,16 @@
       <c r="B22" t="n">
         <v>12</v>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C22" s="8" t="n">
         <v>32.46</v>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="8" t="n">
         <v>12.61</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="8" t="n">
         <v>51.74</v>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="F22" s="9" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -15579,16 +16194,16 @@
       <c r="B23" t="n">
         <v>11</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" s="8" t="n">
         <v>39.79454545454546</v>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="8" t="n">
         <v>23.21</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="8" t="n">
         <v>56.88</v>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="F23" s="9" t="n">
         <v>0.2727272727272727</v>
       </c>
     </row>
@@ -15601,16 +16216,16 @@
       <c r="B24" t="n">
         <v>11</v>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="8" t="n">
         <v>33.55818181818182</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="8" t="n">
         <v>15.94</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="8" t="n">
         <v>58.11</v>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F24" s="9" t="n">
         <v>0.3636363636363636</v>
       </c>
     </row>
@@ -15623,16 +16238,16 @@
       <c r="B25" t="n">
         <v>11</v>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" s="8" t="n">
         <v>31.43363636363636</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="8" t="n">
         <v>12.84</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="8" t="n">
         <v>59.71</v>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="F25" s="9" t="n">
         <v>0.3636363636363636</v>
       </c>
     </row>
@@ -15645,16 +16260,16 @@
       <c r="B26" t="n">
         <v>10</v>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="8" t="n">
         <v>33.501</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="8" t="n">
         <v>11.83</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="8" t="n">
         <v>55.5</v>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="F26" s="9" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -15667,16 +16282,16 @@
       <c r="B27" t="n">
         <v>9</v>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C27" s="8" t="n">
         <v>37.05333333333333</v>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" s="8" t="n">
         <v>10.93</v>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" s="8" t="n">
         <v>59.04</v>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="F27" s="9" t="n">
         <v>0.4444444444444444</v>
       </c>
     </row>
@@ -15689,16 +16304,16 @@
       <c r="B28" t="n">
         <v>8</v>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C28" s="8" t="n">
         <v>38.52</v>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" s="8" t="n">
         <v>10.29</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" s="8" t="n">
         <v>49.05</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="F28" s="9" t="n">
         <v>0.625</v>
       </c>
     </row>
@@ -15711,16 +16326,16 @@
       <c r="B29" t="n">
         <v>7</v>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C29" s="8" t="n">
         <v>32.56714285714286</v>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D29" s="8" t="n">
         <v>21.87</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" s="8" t="n">
         <v>57.49</v>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="F29" s="9" t="n">
         <v>0.4285714285714285</v>
       </c>
     </row>
@@ -15733,16 +16348,16 @@
       <c r="B30" t="n">
         <v>7</v>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C30" s="8" t="n">
         <v>34.21857142857143</v>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D30" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" s="8" t="n">
         <v>59.95</v>
       </c>
-      <c r="F30" s="3" t="n">
+      <c r="F30" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15755,16 +16370,16 @@
       <c r="B31" t="n">
         <v>6</v>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C31" s="8" t="n">
         <v>46.38333333333333</v>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" s="8" t="n">
         <v>36.29</v>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E31" s="8" t="n">
         <v>58.35</v>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="F31" s="9" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -15777,16 +16392,16 @@
       <c r="B32" t="n">
         <v>6</v>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C32" s="8" t="n">
         <v>34.385</v>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="8" t="n">
         <v>17.97</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="8" t="n">
         <v>49.97</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="9" t="n">
         <v>0.8333333333333334</v>
       </c>
     </row>
@@ -15799,16 +16414,16 @@
       <c r="B33" t="n">
         <v>6</v>
       </c>
-      <c r="C33" s="2" t="n">
+      <c r="C33" s="8" t="n">
         <v>35.09833333333334</v>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D33" s="8" t="n">
         <v>17.66</v>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E33" s="8" t="n">
         <v>55.65</v>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="F33" s="9" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -15821,16 +16436,16 @@
       <c r="B34" t="n">
         <v>5</v>
       </c>
-      <c r="C34" s="2" t="n">
+      <c r="C34" s="8" t="n">
         <v>41.166</v>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D34" s="8" t="n">
         <v>24.42</v>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E34" s="8" t="n">
         <v>51.22</v>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -15843,16 +16458,16 @@
       <c r="B35" t="n">
         <v>5</v>
       </c>
-      <c r="C35" s="2" t="n">
+      <c r="C35" s="8" t="n">
         <v>33.662</v>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D35" s="8" t="n">
         <v>16.85</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E35" s="8" t="n">
         <v>48.19</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15865,16 +16480,16 @@
       <c r="B36" t="n">
         <v>5</v>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C36" s="8" t="n">
         <v>40.62</v>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="8" t="n">
         <v>12.08</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="8" t="n">
         <v>52.15</v>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="F36" s="9" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -15887,16 +16502,16 @@
       <c r="B37" t="n">
         <v>4</v>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C37" s="8" t="n">
         <v>51.4525</v>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D37" s="8" t="n">
         <v>49.05</v>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E37" s="8" t="n">
         <v>54.07</v>
       </c>
-      <c r="F37" s="3" t="n">
+      <c r="F37" s="9" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -15909,16 +16524,16 @@
       <c r="B38" t="n">
         <v>3</v>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C38" s="8" t="n">
         <v>36.2</v>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D38" s="8" t="n">
         <v>24.04</v>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" s="8" t="n">
         <v>52.79</v>
       </c>
-      <c r="F38" s="3" t="n">
+      <c r="F38" s="9" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -15931,16 +16546,16 @@
       <c r="B39" t="n">
         <v>3</v>
       </c>
-      <c r="C39" s="2" t="n">
+      <c r="C39" s="8" t="n">
         <v>42.49666666666666</v>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D39" s="8" t="n">
         <v>25.77</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="F39" s="9" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -15953,16 +16568,16 @@
       <c r="B40" t="n">
         <v>3</v>
       </c>
-      <c r="C40" s="2" t="n">
+      <c r="C40" s="8" t="n">
         <v>53.61333333333332</v>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="D40" s="8" t="n">
         <v>51.33</v>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="E40" s="8" t="n">
         <v>56.86</v>
       </c>
-      <c r="F40" s="3" t="n">
+      <c r="F40" s="9" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -15975,16 +16590,16 @@
       <c r="B41" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="2" t="n">
+      <c r="C41" s="8" t="n">
         <v>22.83</v>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="D41" s="8" t="n">
         <v>15.79</v>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="E41" s="8" t="n">
         <v>29.87</v>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="F41" s="9" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -15997,16 +16612,16 @@
       <c r="B42" t="n">
         <v>1</v>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="C42" s="8" t="n">
         <v>15.4</v>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="8" t="n">
         <v>15.4</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="8" t="n">
         <v>15.4</v>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="F42" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16019,16 +16634,16 @@
       <c r="B43" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="2" t="n">
+      <c r="C43" s="8" t="n">
         <v>37.35</v>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D43" s="8" t="n">
         <v>37.35</v>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E43" s="8" t="n">
         <v>37.35</v>
       </c>
-      <c r="F43" s="3" t="n">
+      <c r="F43" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16041,16 +16656,16 @@
       <c r="B44" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="2" t="n">
+      <c r="C44" s="8" t="n">
         <v>15.36</v>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="D44" s="8" t="n">
         <v>15.36</v>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="E44" s="8" t="n">
         <v>15.36</v>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16063,16 +16678,16 @@
       <c r="B45" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="2" t="n">
+      <c r="C45" s="8" t="n">
         <v>13.12</v>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D45" s="8" t="n">
         <v>13.12</v>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="E45" s="8" t="n">
         <v>13.12</v>
       </c>
-      <c r="F45" s="3" t="n">
+      <c r="F45" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16085,16 +16700,16 @@
       <c r="B46" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C46" s="8" t="n">
         <v>58.33</v>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D46" s="8" t="n">
         <v>58.33</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" s="8" t="n">
         <v>58.33</v>
       </c>
-      <c r="F46" s="3" t="n">
+      <c r="F46" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16107,16 +16722,16 @@
       <c r="B47" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C47" s="8" t="n">
         <v>35.88</v>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D47" s="8" t="n">
         <v>35.88</v>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E47" s="8" t="n">
         <v>35.88</v>
       </c>
-      <c r="F47" s="3" t="n">
+      <c r="F47" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16129,16 +16744,16 @@
       <c r="B48" t="n">
         <v>1</v>
       </c>
-      <c r="C48" s="2" t="n">
+      <c r="C48" s="8" t="n">
         <v>54.81</v>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" s="8" t="n">
         <v>54.81</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E48" s="8" t="n">
         <v>54.81</v>
       </c>
-      <c r="F48" s="3" t="n">
+      <c r="F48" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16151,16 +16766,16 @@
       <c r="B49" t="n">
         <v>1</v>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C49" s="8" t="n">
         <v>36.58</v>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D49" s="8" t="n">
         <v>36.58</v>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E49" s="8" t="n">
         <v>36.58</v>
       </c>
-      <c r="F49" s="3" t="n">
+      <c r="F49" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16173,16 +16788,16 @@
       <c r="B50" t="n">
         <v>1</v>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C50" s="8" t="n">
         <v>19.19</v>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D50" s="8" t="n">
         <v>19.19</v>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="E50" s="8" t="n">
         <v>19.19</v>
       </c>
-      <c r="F50" s="3" t="n">
+      <c r="F50" s="9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16195,26 +16810,43 @@
       <c r="B51" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="2" t="n">
+      <c r="C51" s="8" t="n">
         <v>10.97</v>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D51" s="8" t="n">
         <v>10.97</v>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="E51" s="8" t="n">
         <v>10.97</v>
       </c>
-      <c r="F51" s="3" t="n">
+      <c r="F51" s="9" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B51">
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="002E86AB"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F51">
+    <cfRule type="dataBar" priority="2">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="00F18F01"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16228,12 +16860,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
